--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="O74" t="n">
-        <v>6.3</v>
+        <v>3.37</v>
       </c>
       <c r="P74" t="n">
-        <v>16</v>
+        <v>3.44</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O99" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P99" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="O50" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="P50" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="O51" t="n">
-        <v>3.63</v>
+        <v>5.45</v>
       </c>
       <c r="P51" t="n">
-        <v>3.93</v>
+        <v>7.9</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="O55" t="n">
-        <v>3.91</v>
+        <v>4.35</v>
       </c>
       <c r="P55" t="n">
-        <v>3.97</v>
+        <v>5.8</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O100" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P100" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.46</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="O48" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="P48" t="n">
-        <v>3.85</v>
+        <v>4.72</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="O50" t="n">
-        <v>3.63</v>
+        <v>4.35</v>
       </c>
       <c r="P50" t="n">
-        <v>3.93</v>
+        <v>5.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="O51" t="n">
-        <v>5.45</v>
+        <v>3.91</v>
       </c>
       <c r="P51" t="n">
-        <v>7.9</v>
+        <v>3.97</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>3.33</v>
+        <v>3.63</v>
       </c>
       <c r="P52" t="n">
-        <v>3.12</v>
+        <v>3.93</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="O54" t="n">
-        <v>3.8</v>
+        <v>5.45</v>
       </c>
       <c r="P54" t="n">
-        <v>4.72</v>
+        <v>7.9</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.49</v>
+        <v>2.09</v>
       </c>
       <c r="O55" t="n">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.07</v>
+        <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>3.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P24" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.68</v>
+        <v>2.43</v>
       </c>
       <c r="O48" t="n">
-        <v>3.8</v>
+        <v>3.31</v>
       </c>
       <c r="P48" t="n">
-        <v>4.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="O49" t="n">
-        <v>3.34</v>
+        <v>4.35</v>
       </c>
       <c r="P49" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="O50" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P50" t="n">
-        <v>5.8</v>
+        <v>4.72</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="O52" t="n">
-        <v>3.63</v>
+        <v>3.91</v>
       </c>
       <c r="P52" t="n">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
         <v>2</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="O53" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="P53" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="O55" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="P55" t="n">
-        <v>3.15</v>
+        <v>3.93</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="O56" t="n">
-        <v>3.33</v>
+        <v>5.45</v>
       </c>
       <c r="P56" t="n">
-        <v>3.12</v>
+        <v>7.9</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.29</v>
+        <v>1.27</v>
       </c>
       <c r="O73" t="n">
-        <v>2.93</v>
+        <v>4.65</v>
       </c>
       <c r="P73" t="n">
-        <v>3.47</v>
+        <v>7.45</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.07</v>
+        <v>3.16</v>
       </c>
       <c r="O4" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>3.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.46</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O37" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="P37" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="O48" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="P48" t="n">
-        <v>2.84</v>
+        <v>3.97</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="O49" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P49" t="n">
-        <v>5.8</v>
+        <v>4.72</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="O50" t="n">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="P50" t="n">
-        <v>4.72</v>
+        <v>5.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="O52" t="n">
-        <v>3.91</v>
+        <v>3.34</v>
       </c>
       <c r="P52" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB52" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="O53" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="P53" t="n">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="O55" t="n">
-        <v>3.63</v>
+        <v>5.45</v>
       </c>
       <c r="P55" t="n">
-        <v>3.93</v>
+        <v>7.9</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="O56" t="n">
-        <v>5.45</v>
+        <v>3.63</v>
       </c>
       <c r="P56" t="n">
-        <v>7.9</v>
+        <v>3.93</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="O72" t="n">
-        <v>3.37</v>
+        <v>6.3</v>
       </c>
       <c r="P72" t="n">
-        <v>3.44</v>
+        <v>16</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>7.45</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="O74" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="P74" t="n">
-        <v>3.47</v>
+        <v>4.39</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="O97" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="P97" t="n">
-        <v>3.54</v>
+        <v>2.76</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.46</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>3.33</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O25" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5975,10 +5975,10 @@
         <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="P35" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.68</v>
+        <v>2.43</v>
       </c>
       <c r="O49" t="n">
-        <v>3.8</v>
+        <v>3.31</v>
       </c>
       <c r="P49" t="n">
-        <v>4.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
-        <v>4.35</v>
+        <v>3.33</v>
       </c>
       <c r="P50" t="n">
-        <v>5.8</v>
+        <v>3.12</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.43</v>
+        <v>1.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3.31</v>
+        <v>5.45</v>
       </c>
       <c r="P53" t="n">
-        <v>2.84</v>
+        <v>7.9</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="O54" t="n">
-        <v>3.33</v>
+        <v>4.35</v>
       </c>
       <c r="P54" t="n">
-        <v>3.12</v>
+        <v>5.8</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.3</v>
+        <v>2.09</v>
       </c>
       <c r="O55" t="n">
-        <v>5.45</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>7.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="O56" t="n">
-        <v>3.63</v>
+        <v>3.91</v>
       </c>
       <c r="P56" t="n">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
         <v>2</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="O58" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="P58" t="n">
-        <v>3.15</v>
+        <v>3.93</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.22</v>
+        <v>2.76</v>
       </c>
       <c r="O72" t="n">
-        <v>6.3</v>
+        <v>2.68</v>
       </c>
       <c r="P72" t="n">
-        <v>16</v>
+        <v>2.68</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11888,10 +11888,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.82</v>
+        <v>2.29</v>
       </c>
       <c r="O74" t="n">
-        <v>3.38</v>
+        <v>2.93</v>
       </c>
       <c r="P74" t="n">
-        <v>4.39</v>
+        <v>3.47</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1.27</v>
+        <v>2.66</v>
       </c>
       <c r="O76" t="n">
-        <v>4.65</v>
+        <v>2.67</v>
       </c>
       <c r="P76" t="n">
-        <v>7.45</v>
+        <v>2.78</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="O77" t="n">
-        <v>3.37</v>
+        <v>2.74</v>
       </c>
       <c r="P77" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O98" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P98" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.15</v>
+        <v>3.19</v>
       </c>
       <c r="O100" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="P100" t="n">
-        <v>3.54</v>
+        <v>2.36</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.46</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>3.33</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="P35" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="O49" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P49" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="O50" t="n">
-        <v>3.33</v>
+        <v>3.91</v>
       </c>
       <c r="P50" t="n">
-        <v>3.12</v>
+        <v>3.97</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="O54" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P54" t="n">
-        <v>5.8</v>
+        <v>4.72</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="O55" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P55" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="O56" t="n">
-        <v>3.91</v>
+        <v>4.35</v>
       </c>
       <c r="P56" t="n">
-        <v>3.97</v>
+        <v>5.8</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="O57" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="P57" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,49 +9629,49 @@
         </is>
       </c>
       <c r="N58" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB58" t="n">
         <v>1.85</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="P58" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.27</v>
+        <v>2.46</v>
       </c>
       <c r="O67" t="n">
-        <v>4.65</v>
+        <v>2.74</v>
       </c>
       <c r="P67" t="n">
-        <v>7.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="O68" t="n">
-        <v>3.38</v>
+        <v>2.64</v>
       </c>
       <c r="P68" t="n">
-        <v>4.39</v>
+        <v>3.55</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,16 +11252,16 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.28</v>
+        <v>1.27</v>
       </c>
       <c r="O71" t="n">
-        <v>2.64</v>
+        <v>4.65</v>
       </c>
       <c r="P71" t="n">
-        <v>3.55</v>
+        <v>7.45</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,16 +11729,16 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="O74" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="P74" t="n">
-        <v>3.47</v>
+        <v>4.39</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.66</v>
+        <v>2.29</v>
       </c>
       <c r="O76" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="P76" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="O77" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="P77" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13130,10 +13130,10 @@
         <v>2.16</v>
       </c>
       <c r="O80" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="P80" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13289,10 +13289,10 @@
         <v>2.16</v>
       </c>
       <c r="O81" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="P81" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="O84" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="P84" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="O99" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="P99" t="n">
-        <v>2.76</v>
+        <v>3.54</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU101"/>
+  <dimension ref="A1:AU102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5816,10 +5816,10 @@
         <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="O50" t="n">
-        <v>3.91</v>
+        <v>3.31</v>
       </c>
       <c r="P50" t="n">
-        <v>3.97</v>
+        <v>2.84</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB50" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="O52" t="n">
-        <v>5.45</v>
+        <v>3.34</v>
       </c>
       <c r="P52" t="n">
-        <v>7.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="O55" t="n">
-        <v>3.33</v>
+        <v>3.91</v>
       </c>
       <c r="P55" t="n">
-        <v>3.12</v>
+        <v>3.97</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="O56" t="n">
-        <v>4.35</v>
+        <v>5.45</v>
       </c>
       <c r="P56" t="n">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="O57" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="P57" t="n">
-        <v>3.93</v>
+        <v>3.15</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="O58" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="P58" t="n">
-        <v>3.85</v>
+        <v>4.72</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9741,27 +9741,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="60">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="O63" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="P63" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46173.625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10695,12 +10695,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46173.64583333334</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="66">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="O67" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="P67" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.64583333334</v>
       </c>
     </row>
     <row r="68">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="O68" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
       <c r="P68" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.22</v>
+        <v>1.82</v>
       </c>
       <c r="O70" t="n">
-        <v>6.3</v>
+        <v>3.38</v>
       </c>
       <c r="P70" t="n">
-        <v>16</v>
+        <v>4.39</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="O71" t="n">
-        <v>4.65</v>
+        <v>6.3</v>
       </c>
       <c r="P71" t="n">
-        <v>7.45</v>
+        <v>16</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="O72" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="P72" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11888,10 +11888,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12047,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12365,10 +12365,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="AU79" s="3" t="n">
-        <v>46173.67708333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="80">
@@ -13080,12 +13080,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>46173.6875</v>
+        <v>46173.67708333334</v>
       </c>
     </row>
     <row r="81">
@@ -13398,12 +13398,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.6875</v>
       </c>
     </row>
     <row r="83">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>5.3</v>
+        <v>2.13</v>
       </c>
       <c r="O86" t="n">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="P86" t="n">
-        <v>1.55</v>
+        <v>3.56</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46173.72916666666</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="87">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>46173.75</v>
+        <v>46173.72916666666</v>
       </c>
     </row>
     <row r="88">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46173.76041666666</v>
+        <v>46173.75</v>
       </c>
     </row>
     <row r="90">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.76041666666</v>
       </c>
     </row>
     <row r="91">
@@ -15147,12 +15147,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15297,7 +15297,7 @@
         <v>0</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="94">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="AU96" s="3" t="n">
-        <v>46173.84027777778</v>
+        <v>46173.83333333334</v>
       </c>
     </row>
     <row r="97">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="O97" t="n">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="P97" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="AU97" s="3" t="n">
-        <v>46173.85416666666</v>
+        <v>46173.84027777778</v>
       </c>
     </row>
     <row r="98">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3.19</v>
+        <v>2.64</v>
       </c>
       <c r="O100" t="n">
-        <v>3.29</v>
+        <v>2.96</v>
       </c>
       <c r="P100" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16419,156 +16419,315 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O101" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P101" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" s="3" t="n">
+        <v>46173.85416666666</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>Palestino</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Audax Italiano</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="inlineStr">
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU101" s="3" t="n">
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" s="3" t="n">
         <v>46173.875</v>
       </c>
     </row>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.07</v>
+        <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>3.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5816,10 +5816,10 @@
         <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O43" t="n">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
       <c r="P43" t="n">
-        <v>3.13</v>
+        <v>3.39</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.23</v>
+        <v>1.26</v>
       </c>
       <c r="O45" t="n">
-        <v>3.5</v>
+        <v>5.99</v>
       </c>
       <c r="P45" t="n">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="O53" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P53" t="n">
-        <v>5.8</v>
+        <v>4.72</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="O55" t="n">
-        <v>3.91</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.68</v>
+        <v>2.43</v>
       </c>
       <c r="O58" t="n">
-        <v>3.8</v>
+        <v>3.31</v>
       </c>
       <c r="P58" t="n">
-        <v>4.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>6.34</v>
+        <v>2.68</v>
       </c>
       <c r="O61" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="P61" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,14 +10901,14 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="O66" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P66" t="n">
         <v>2.7</v>
       </c>
-      <c r="P66" t="n">
-        <v>2.91</v>
-      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O67" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="O69" t="n">
-        <v>3.37</v>
+        <v>2.74</v>
       </c>
       <c r="P69" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.82</v>
+        <v>2.66</v>
       </c>
       <c r="O70" t="n">
-        <v>3.38</v>
+        <v>2.67</v>
       </c>
       <c r="P70" t="n">
-        <v>4.39</v>
+        <v>2.78</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.22</v>
+        <v>2.29</v>
       </c>
       <c r="O71" t="n">
-        <v>6.3</v>
+        <v>2.93</v>
       </c>
       <c r="P71" t="n">
-        <v>16</v>
+        <v>3.47</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="O75" t="n">
-        <v>2.64</v>
+        <v>3.38</v>
       </c>
       <c r="P75" t="n">
-        <v>3.55</v>
+        <v>4.39</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12365,16 +12365,16 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="O78" t="n">
-        <v>4.65</v>
+        <v>6.3</v>
       </c>
       <c r="P78" t="n">
-        <v>7.45</v>
+        <v>16</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13289,10 +13289,10 @@
         <v>2.16</v>
       </c>
       <c r="O81" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="P81" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13448,10 +13448,10 @@
         <v>2.16</v>
       </c>
       <c r="O82" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="P82" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="O84" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="P84" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O98" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P98" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.64</v>
+        <v>3.19</v>
       </c>
       <c r="O100" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="P100" t="n">
-        <v>2.76</v>
+        <v>2.36</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.46</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O25" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>2.81</v>
+        <v>3.31</v>
       </c>
       <c r="P36" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.83</v>
+        <v>3.23</v>
       </c>
       <c r="O39" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P39" t="n">
-        <v>4.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O40" t="n">
-        <v>3.87</v>
+        <v>3.35</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>3.13</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.23</v>
+        <v>1.91</v>
       </c>
       <c r="O41" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="P41" t="n">
-        <v>2.06</v>
+        <v>3.39</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.81</v>
+        <v>1.26</v>
       </c>
       <c r="O42" t="n">
-        <v>3.85</v>
+        <v>5.99</v>
       </c>
       <c r="P42" t="n">
-        <v>2.19</v>
+        <v>8</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.91</v>
+        <v>2.81</v>
       </c>
       <c r="O43" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="P43" t="n">
-        <v>3.39</v>
+        <v>2.19</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.98</v>
+        <v>1.83</v>
       </c>
       <c r="O44" t="n">
-        <v>3.72</v>
+        <v>3.46</v>
       </c>
       <c r="P44" t="n">
-        <v>2.13</v>
+        <v>4.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.26</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
-        <v>5.99</v>
+        <v>3.72</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>2.13</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
-        <v>3.35</v>
+        <v>3.87</v>
       </c>
       <c r="P46" t="n">
-        <v>3.13</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.49</v>
+        <v>1.78</v>
       </c>
       <c r="O48" t="n">
-        <v>4.35</v>
+        <v>3.91</v>
       </c>
       <c r="P48" t="n">
-        <v>5.8</v>
+        <v>3.97</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="O49" t="n">
-        <v>3.91</v>
+        <v>3.33</v>
       </c>
       <c r="P49" t="n">
-        <v>3.97</v>
+        <v>3.12</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="O51" t="n">
-        <v>3.33</v>
+        <v>4.35</v>
       </c>
       <c r="P51" t="n">
-        <v>3.12</v>
+        <v>5.8</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.85</v>
+        <v>2.43</v>
       </c>
       <c r="O54" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="P54" t="n">
-        <v>3.93</v>
+        <v>2.84</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="O56" t="n">
-        <v>5.45</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>7.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="O57" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="P57" t="n">
-        <v>3.15</v>
+        <v>3.93</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="O58" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P58" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O66" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P66" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,14 +11060,14 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="O67" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P67" t="n">
         <v>2.7</v>
       </c>
-      <c r="P67" t="n">
-        <v>2.91</v>
-      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="O69" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="P69" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O70" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="P70" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11570,10 +11570,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.29</v>
+        <v>2.46</v>
       </c>
       <c r="O71" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="P71" t="n">
-        <v>3.47</v>
+        <v>3.05</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12047,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="O74" t="n">
-        <v>3.37</v>
+        <v>4.65</v>
       </c>
       <c r="P74" t="n">
-        <v>3.44</v>
+        <v>7.45</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="O75" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="P75" t="n">
-        <v>4.39</v>
+        <v>3.44</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="O76" t="n">
-        <v>2.64</v>
+        <v>3.38</v>
       </c>
       <c r="P76" t="n">
-        <v>3.55</v>
+        <v>4.39</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,16 +12524,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.27</v>
+        <v>2.29</v>
       </c>
       <c r="O77" t="n">
-        <v>4.65</v>
+        <v>2.93</v>
       </c>
       <c r="P77" t="n">
-        <v>7.45</v>
+        <v>3.47</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>3.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P23" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="O36" t="n">
-        <v>3.31</v>
+        <v>5.1</v>
       </c>
       <c r="P36" t="n">
-        <v>3.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>2.81</v>
+        <v>3.31</v>
       </c>
       <c r="P37" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3.23</v>
+        <v>2.15</v>
       </c>
       <c r="O39" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>3.13</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="O40" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="P40" t="n">
-        <v>3.13</v>
+        <v>2.19</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.91</v>
+        <v>3.23</v>
       </c>
       <c r="O41" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P41" t="n">
-        <v>3.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.81</v>
+        <v>1.91</v>
       </c>
       <c r="O43" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="P43" t="n">
-        <v>2.19</v>
+        <v>3.39</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="O48" t="n">
-        <v>3.91</v>
+        <v>3.31</v>
       </c>
       <c r="P48" t="n">
-        <v>3.97</v>
+        <v>2.84</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB48" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="O49" t="n">
-        <v>3.33</v>
+        <v>3.91</v>
       </c>
       <c r="P49" t="n">
-        <v>3.12</v>
+        <v>3.97</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="O54" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P54" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="P56" t="n">
-        <v>3.85</v>
+        <v>3.12</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,49 +9470,49 @@
         </is>
       </c>
       <c r="N57" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P57" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB57" t="n">
         <v>1.85</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="P57" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="O58" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P58" t="n">
-        <v>3.15</v>
+        <v>4.72</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11570,10 +11570,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="O71" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="P71" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O72" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="P72" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11888,10 +11888,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="O74" t="n">
-        <v>4.65</v>
+        <v>3.37</v>
       </c>
       <c r="P74" t="n">
-        <v>7.45</v>
+        <v>3.44</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="O75" t="n">
-        <v>3.37</v>
+        <v>2.93</v>
       </c>
       <c r="P75" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1.82</v>
+        <v>2.66</v>
       </c>
       <c r="O76" t="n">
-        <v>3.38</v>
+        <v>2.67</v>
       </c>
       <c r="P76" t="n">
-        <v>4.39</v>
+        <v>2.78</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="O85" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="P85" t="n">
-        <v>3.05</v>
+        <v>3.63</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="O98" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="P98" t="n">
-        <v>3.54</v>
+        <v>2.76</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O100" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P100" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.46</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>3.33</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O24" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P24" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5816,10 +5816,10 @@
         <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6293,10 +6293,10 @@
         <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.15</v>
+        <v>3.23</v>
       </c>
       <c r="O39" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P39" t="n">
-        <v>3.13</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.81</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="P40" t="n">
-        <v>2.19</v>
+        <v>3.39</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.23</v>
+        <v>1.83</v>
       </c>
       <c r="O41" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P41" t="n">
-        <v>2.06</v>
+        <v>4.15</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.26</v>
+        <v>2.81</v>
       </c>
       <c r="O42" t="n">
-        <v>5.99</v>
+        <v>3.85</v>
       </c>
       <c r="P42" t="n">
-        <v>8</v>
+        <v>2.19</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.91</v>
+        <v>2.98</v>
       </c>
       <c r="O43" t="n">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="P43" t="n">
-        <v>3.39</v>
+        <v>2.13</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="O44" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="P44" t="n">
-        <v>4.15</v>
+        <v>3.13</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>1.26</v>
       </c>
       <c r="O45" t="n">
-        <v>3.72</v>
+        <v>5.99</v>
       </c>
       <c r="P45" t="n">
-        <v>2.13</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.43</v>
+        <v>1.96</v>
       </c>
       <c r="O48" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="P48" t="n">
-        <v>2.84</v>
+        <v>3.85</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="O49" t="n">
-        <v>3.91</v>
+        <v>5.45</v>
       </c>
       <c r="P49" t="n">
-        <v>3.97</v>
+        <v>7.9</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.3</v>
+        <v>2.09</v>
       </c>
       <c r="O53" t="n">
-        <v>5.45</v>
+        <v>3.4</v>
       </c>
       <c r="P53" t="n">
-        <v>7.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="O54" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P54" t="n">
-        <v>3.15</v>
+        <v>4.72</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="O57" t="n">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="P57" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.68</v>
+        <v>2.43</v>
       </c>
       <c r="O58" t="n">
-        <v>3.8</v>
+        <v>3.31</v>
       </c>
       <c r="P58" t="n">
-        <v>4.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,14 +10901,14 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="O66" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P66" t="n">
         <v>2.7</v>
       </c>
-      <c r="P66" t="n">
-        <v>2.91</v>
-      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O67" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P67" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.76</v>
+        <v>1.27</v>
       </c>
       <c r="O72" t="n">
-        <v>2.68</v>
+        <v>4.65</v>
       </c>
       <c r="P72" t="n">
-        <v>2.68</v>
+        <v>7.45</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11888,16 +11888,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>7.45</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="O74" t="n">
-        <v>3.37</v>
+        <v>2.74</v>
       </c>
       <c r="P74" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.29</v>
+        <v>2.76</v>
       </c>
       <c r="O75" t="n">
-        <v>2.93</v>
+        <v>2.68</v>
       </c>
       <c r="P75" t="n">
-        <v>3.47</v>
+        <v>2.68</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12365,10 +12365,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.66</v>
+        <v>1.82</v>
       </c>
       <c r="O76" t="n">
-        <v>2.67</v>
+        <v>3.38</v>
       </c>
       <c r="P76" t="n">
-        <v>2.78</v>
+        <v>4.39</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12848,10 +12848,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2.46</v>
+        <v>1.22</v>
       </c>
       <c r="O79" t="n">
-        <v>2.74</v>
+        <v>6.3</v>
       </c>
       <c r="P79" t="n">
-        <v>3.05</v>
+        <v>16</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="O83" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="P83" t="n">
-        <v>3.05</v>
+        <v>3.63</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="O84" t="n">
-        <v>2.86</v>
+        <v>3.13</v>
       </c>
       <c r="P84" t="n">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="O85" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="P85" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>2.81</v>
+        <v>3.31</v>
       </c>
       <c r="P35" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3.23</v>
+        <v>1.91</v>
       </c>
       <c r="O39" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>3.39</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O40" t="n">
-        <v>3.88</v>
+        <v>3.46</v>
       </c>
       <c r="P40" t="n">
-        <v>3.39</v>
+        <v>4.15</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="O41" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="P41" t="n">
-        <v>4.15</v>
+        <v>3.13</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.81</v>
+        <v>3.23</v>
       </c>
       <c r="O42" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.98</v>
+        <v>1.26</v>
       </c>
       <c r="O43" t="n">
-        <v>3.72</v>
+        <v>5.99</v>
       </c>
       <c r="P43" t="n">
-        <v>2.13</v>
+        <v>8</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
-        <v>3.35</v>
+        <v>3.87</v>
       </c>
       <c r="P44" t="n">
-        <v>3.13</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.26</v>
+        <v>2.81</v>
       </c>
       <c r="O45" t="n">
-        <v>5.99</v>
+        <v>3.85</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>2.19</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="O46" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="P46" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="O50" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="P50" t="n">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="O51" t="n">
-        <v>4.35</v>
+        <v>3.33</v>
       </c>
       <c r="P51" t="n">
-        <v>5.8</v>
+        <v>3.12</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="O52" t="n">
-        <v>3.91</v>
+        <v>4.35</v>
       </c>
       <c r="P52" t="n">
-        <v>3.97</v>
+        <v>5.8</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.09</v>
+        <v>1.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3.4</v>
+        <v>5.45</v>
       </c>
       <c r="P53" t="n">
-        <v>3.15</v>
+        <v>7.9</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="O54" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="P54" t="n">
-        <v>4.72</v>
+        <v>3.97</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.43</v>
+        <v>1.68</v>
       </c>
       <c r="O58" t="n">
-        <v>3.31</v>
+        <v>3.8</v>
       </c>
       <c r="P58" t="n">
-        <v>2.84</v>
+        <v>4.72</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>6.34</v>
+        <v>2.68</v>
       </c>
       <c r="O60" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="P60" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="O69" t="n">
-        <v>3.37</v>
+        <v>2.67</v>
       </c>
       <c r="P69" t="n">
-        <v>3.44</v>
+        <v>2.78</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.27</v>
+        <v>2.29</v>
       </c>
       <c r="O72" t="n">
-        <v>4.65</v>
+        <v>2.93</v>
       </c>
       <c r="P72" t="n">
-        <v>7.45</v>
+        <v>3.47</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="O74" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="P74" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12365,10 +12365,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="O77" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="P77" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13289,10 +13289,10 @@
         <v>2.16</v>
       </c>
       <c r="O81" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="P81" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13448,10 +13448,10 @@
         <v>2.16</v>
       </c>
       <c r="O82" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="P82" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="O84" t="n">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="P84" t="n">
-        <v>3.05</v>
+        <v>3.56</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="O85" t="n">
-        <v>2.86</v>
+        <v>3.13</v>
       </c>
       <c r="P85" t="n">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.64</v>
+        <v>3.19</v>
       </c>
       <c r="O98" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="P98" t="n">
-        <v>2.76</v>
+        <v>2.36</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="O99" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="P99" t="n">
-        <v>3.54</v>
+        <v>2.76</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>3.33</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>8.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="O39" t="n">
-        <v>3.88</v>
+        <v>3.35</v>
       </c>
       <c r="P39" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.83</v>
+        <v>2.98</v>
       </c>
       <c r="O40" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="P40" t="n">
-        <v>4.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="O41" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P41" t="n">
-        <v>3.13</v>
+        <v>4.15</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3.5</v>
+        <v>3.87</v>
       </c>
       <c r="P42" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>1.91</v>
       </c>
       <c r="O44" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="P44" t="n">
-        <v>1.8</v>
+        <v>3.39</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.81</v>
+        <v>3.23</v>
       </c>
       <c r="O45" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P45" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="O46" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="P46" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="O51" t="n">
-        <v>3.33</v>
+        <v>3.91</v>
       </c>
       <c r="P51" t="n">
-        <v>3.12</v>
+        <v>3.97</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="O52" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P52" t="n">
-        <v>5.8</v>
+        <v>4.72</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.3</v>
+        <v>2.09</v>
       </c>
       <c r="O53" t="n">
-        <v>5.45</v>
+        <v>3.4</v>
       </c>
       <c r="P53" t="n">
-        <v>7.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="O54" t="n">
-        <v>3.91</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB54" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="O56" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P56" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="O57" t="n">
-        <v>3.63</v>
+        <v>5.45</v>
       </c>
       <c r="P57" t="n">
-        <v>3.93</v>
+        <v>7.9</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="O64" t="n">
         <v>3.3</v>
       </c>
       <c r="P64" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="O65" t="n">
         <v>3.3</v>
       </c>
       <c r="P65" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="O68" t="n">
-        <v>3.37</v>
+        <v>2.68</v>
       </c>
       <c r="P68" t="n">
-        <v>3.44</v>
+        <v>2.68</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.66</v>
+        <v>2.29</v>
       </c>
       <c r="O69" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="P69" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.27</v>
+        <v>2.46</v>
       </c>
       <c r="O73" t="n">
-        <v>4.65</v>
+        <v>2.74</v>
       </c>
       <c r="P73" t="n">
-        <v>7.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="O74" t="n">
-        <v>2.64</v>
+        <v>3.38</v>
       </c>
       <c r="P74" t="n">
-        <v>3.55</v>
+        <v>4.39</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12206,16 +12206,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="O76" t="n">
-        <v>3.38</v>
+        <v>2.64</v>
       </c>
       <c r="P76" t="n">
-        <v>4.39</v>
+        <v>3.55</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,16 +12524,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="O77" t="n">
-        <v>2.74</v>
+        <v>3.37</v>
       </c>
       <c r="P77" t="n">
-        <v>3.05</v>
+        <v>3.44</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="O79" t="n">
-        <v>6.3</v>
+        <v>4.65</v>
       </c>
       <c r="P79" t="n">
-        <v>16</v>
+        <v>7.45</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13289,10 +13289,10 @@
         <v>2.16</v>
       </c>
       <c r="O81" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="P81" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13448,10 +13448,10 @@
         <v>2.16</v>
       </c>
       <c r="O82" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="P82" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="O85" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="P85" t="n">
-        <v>3.05</v>
+        <v>3.63</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.15</v>
+        <v>3.19</v>
       </c>
       <c r="O100" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="P100" t="n">
-        <v>3.54</v>
+        <v>2.36</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU102"/>
+  <dimension ref="A1:AU107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.07</v>
+        <v>3.16</v>
       </c>
       <c r="O4" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>3.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>3.33</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>2.81</v>
+        <v>3.31</v>
       </c>
       <c r="P36" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O39" t="n">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
       <c r="P39" t="n">
-        <v>3.13</v>
+        <v>3.39</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.83</v>
+        <v>2.98</v>
       </c>
       <c r="O41" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="P41" t="n">
-        <v>4.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O42" t="n">
-        <v>3.87</v>
+        <v>3.35</v>
       </c>
       <c r="P42" t="n">
-        <v>1.8</v>
+        <v>3.13</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.91</v>
+        <v>3.23</v>
       </c>
       <c r="O44" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P44" t="n">
-        <v>3.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.23</v>
+        <v>1.26</v>
       </c>
       <c r="O45" t="n">
-        <v>3.5</v>
+        <v>5.99</v>
       </c>
       <c r="P45" t="n">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O47" t="n">
-        <v>2.95</v>
+        <v>3.46</v>
       </c>
       <c r="P47" t="n">
-        <v>4.96</v>
+        <v>4.15</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46173.54166666666</v>
+        <v>46173.5</v>
       </c>
     </row>
     <row r="48">
@@ -7992,27 +7992,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="O48" t="n">
-        <v>3.31</v>
+        <v>3.87</v>
       </c>
       <c r="P48" t="n">
-        <v>2.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.5</v>
       </c>
     </row>
     <row r="49">
@@ -8151,27 +8151,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.49</v>
+        <v>2.81</v>
       </c>
       <c r="O49" t="n">
-        <v>4.35</v>
+        <v>3.85</v>
       </c>
       <c r="P49" t="n">
-        <v>5.8</v>
+        <v>2.19</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.5</v>
       </c>
     </row>
     <row r="50">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.5</v>
       </c>
     </row>
     <row r="51">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
-        <v>3.91</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>3.97</v>
+        <v>2.65</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.5</v>
       </c>
     </row>
     <row r="52">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="O52" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="P52" t="n">
-        <v>4.72</v>
+        <v>4.96</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.54166666666</v>
       </c>
     </row>
     <row r="53">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.09</v>
+        <v>1.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3.4</v>
+        <v>5.45</v>
       </c>
       <c r="P53" t="n">
-        <v>3.15</v>
+        <v>7.9</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="P54" t="n">
-        <v>3.85</v>
+        <v>4.72</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="O55" t="n">
-        <v>3.63</v>
+        <v>4.35</v>
       </c>
       <c r="P55" t="n">
-        <v>3.93</v>
+        <v>5.8</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="O56" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="O57" t="n">
-        <v>5.45</v>
+        <v>3.63</v>
       </c>
       <c r="P57" t="n">
-        <v>7.9</v>
+        <v>3.93</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="61">
@@ -10059,27 +10059,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>6.34</v>
+        <v>2.43</v>
       </c>
       <c r="O61" t="n">
-        <v>4.5</v>
+        <v>3.31</v>
       </c>
       <c r="P61" t="n">
-        <v>1.41</v>
+        <v>2.84</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="62">
@@ -10218,27 +10218,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="63">
@@ -10377,27 +10377,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="64">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46173.625</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="65">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.25</v>
+        <v>6.34</v>
       </c>
       <c r="O65" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="P65" t="n">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46173.625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="66">
@@ -10854,12 +10854,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="O66" t="n">
-        <v>2.61</v>
+        <v>3.68</v>
       </c>
       <c r="P66" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46173.64583333334</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="67">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46173.64583333334</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="68">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="69">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O69" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="P69" t="n">
-        <v>3.47</v>
+        <v>2.75</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="70">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.22</v>
+        <v>2.44</v>
       </c>
       <c r="O70" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="P70" t="n">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="71">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11799,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.64583333334</v>
       </c>
     </row>
     <row r="72">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11958,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.64583333334</v>
       </c>
     </row>
     <row r="73">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.46</v>
+        <v>1.22</v>
       </c>
       <c r="O73" t="n">
-        <v>2.74</v>
+        <v>6.3</v>
       </c>
       <c r="P73" t="n">
-        <v>3.05</v>
+        <v>16</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.82</v>
+        <v>2.66</v>
       </c>
       <c r="O74" t="n">
-        <v>3.38</v>
+        <v>2.67</v>
       </c>
       <c r="P74" t="n">
-        <v>4.39</v>
+        <v>2.78</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="O75" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="P75" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12365,10 +12365,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="O77" t="n">
-        <v>3.37</v>
+        <v>2.74</v>
       </c>
       <c r="P77" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="O79" t="n">
-        <v>4.65</v>
+        <v>3.38</v>
       </c>
       <c r="P79" t="n">
-        <v>7.45</v>
+        <v>4.39</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13080,12 +13080,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13230,7 +13230,7 @@
         <v>0</v>
       </c>
       <c r="AU80" s="3" t="n">
-        <v>46173.67708333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="81">
@@ -13239,12 +13239,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O81" t="n">
-        <v>2.77</v>
+        <v>3.37</v>
       </c>
       <c r="P81" t="n">
-        <v>3.63</v>
+        <v>3.44</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13389,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>46173.6875</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="82">
@@ -13398,12 +13398,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>46173.6875</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="83">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.21</v>
+        <v>1.27</v>
       </c>
       <c r="O83" t="n">
-        <v>3.13</v>
+        <v>4.65</v>
       </c>
       <c r="P83" t="n">
-        <v>3.05</v>
+        <v>7.45</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="84">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="O84" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="P84" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13866,7 +13866,7 @@
         <v>0</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="85">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.67708333334</v>
       </c>
     </row>
     <row r="86">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.6875</v>
       </c>
     </row>
     <row r="87">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>5.3</v>
+        <v>2.16</v>
       </c>
       <c r="O87" t="n">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="P87" t="n">
-        <v>1.55</v>
+        <v>3.63</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>46173.72916666666</v>
+        <v>46173.6875</v>
       </c>
     </row>
     <row r="88">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>46173.75</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="89">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46173.75</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="90">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>46173.76041666666</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="91">
@@ -14829,12 +14829,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="92">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.72916666666</v>
       </c>
     </row>
     <row r="93">
@@ -15147,12 +15147,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15297,7 +15297,7 @@
         <v>0</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.75</v>
       </c>
     </row>
     <row r="94">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="AU94" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.75</v>
       </c>
     </row>
     <row r="95">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15615,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="AU95" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.76041666666</v>
       </c>
     </row>
     <row r="96">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="AU96" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="97">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="AU97" s="3" t="n">
-        <v>46173.84027777778</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="98">
@@ -15942,12 +15942,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="AU98" s="3" t="n">
-        <v>46173.85416666666</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="99">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="O99" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="P99" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16251,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="AU99" s="3" t="n">
-        <v>46173.85416666666</v>
+        <v>46173.83333333334</v>
       </c>
     </row>
     <row r="100">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46173.85416666666</v>
+        <v>46173.83333333334</v>
       </c>
     </row>
     <row r="101">
@@ -16419,12 +16419,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="AU101" s="3" t="n">
-        <v>46173.85416666666</v>
+        <v>46173.83333333334</v>
       </c>
     </row>
     <row r="102">
@@ -16578,156 +16578,951 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>CD Universidad Católica</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O102" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P102" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" s="3" t="n">
+        <v>46173.84027777778</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" s="3" t="n">
+        <v>46173.85416666666</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O104" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P104" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" s="3" t="n">
+        <v>46173.85416666666</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O105" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P105" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" s="3" t="n">
+        <v>46173.85416666666</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O106" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="P106" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" s="3" t="n">
+        <v>46173.85416666666</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Palestino</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Audax Italiano</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="inlineStr">
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO102" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP102" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU102" s="3" t="n">
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" s="3" t="n">
         <v>46173.875</v>
       </c>
     </row>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU107"/>
+  <dimension ref="A1:AU106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>1.32</v>
       </c>
       <c r="O35" t="n">
-        <v>2.81</v>
+        <v>5.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.81</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O36" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="P36" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6458,34 +6458,34 @@
         <v>2.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA38" t="n">
         <v>1.8</v>
@@ -6494,19 +6494,19 @@
         <v>2</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.91</v>
+        <v>2.81</v>
       </c>
       <c r="O39" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="P39" t="n">
-        <v>3.39</v>
+        <v>2.19</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.23</v>
+        <v>1.83</v>
       </c>
       <c r="O44" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P44" t="n">
-        <v>2.06</v>
+        <v>4.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.26</v>
+        <v>3.8</v>
       </c>
       <c r="O45" t="n">
-        <v>5.99</v>
+        <v>3.87</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3.8</v>
+        <v>1.26</v>
       </c>
       <c r="O48" t="n">
-        <v>3.87</v>
+        <v>5.99</v>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="O53" t="n">
-        <v>5.45</v>
+        <v>3.8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.9</v>
+        <v>4.72</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="O55" t="n">
-        <v>4.35</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.09</v>
+        <v>1.3</v>
       </c>
       <c r="O58" t="n">
-        <v>3.4</v>
+        <v>5.45</v>
       </c>
       <c r="P58" t="n">
-        <v>3.15</v>
+        <v>7.9</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="O59" t="n">
-        <v>3.91</v>
+        <v>3.31</v>
       </c>
       <c r="P59" t="n">
-        <v>3.97</v>
+        <v>2.84</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="O61" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="P61" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10218,27 +10218,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -10377,27 +10377,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="65">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>6.34</v>
+        <v>2.68</v>
       </c>
       <c r="O65" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="P65" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="O66" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P66" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="67">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="68">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.64583333334</v>
       </c>
     </row>
     <row r="69">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="P69" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>46173.625</v>
+        <v>46173.64583333334</v>
       </c>
     </row>
     <row r="70">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="O70" t="n">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="P70" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11570,10 +11570,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -11640,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="AU70" s="3" t="n">
-        <v>46173.625</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="71">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="O71" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="P71" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11799,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="AU71" s="3" t="n">
-        <v>46173.64583333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="72">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O72" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="P72" t="n">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11958,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="AU72" s="3" t="n">
-        <v>46173.64583333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="73">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.22</v>
+        <v>2.28</v>
       </c>
       <c r="O73" t="n">
-        <v>6.3</v>
+        <v>2.64</v>
       </c>
       <c r="P73" t="n">
-        <v>16</v>
+        <v>3.55</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12047,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.66</v>
+        <v>2.29</v>
       </c>
       <c r="O74" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="P74" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12365,10 +12365,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.46</v>
+        <v>1.22</v>
       </c>
       <c r="O77" t="n">
-        <v>2.74</v>
+        <v>6.3</v>
       </c>
       <c r="P77" t="n">
-        <v>3.05</v>
+        <v>16</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -12926,22 +12926,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,80 +12968,80 @@
         </is>
       </c>
       <c r="N79" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O79" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK79" t="n">
         <v>1.82</v>
-      </c>
-      <c r="O79" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P79" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>0</v>
       </c>
       <c r="AL79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="O81" t="n">
-        <v>3.37</v>
+        <v>4.65</v>
       </c>
       <c r="P81" t="n">
-        <v>3.44</v>
+        <v>7.45</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13325,10 +13325,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -13403,22 +13403,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,64 +13445,64 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13515,10 +13515,10 @@
         </is>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>7.45</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13643,10 +13643,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="O84" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="P84" t="n">
-        <v>3.47</v>
+        <v>4.39</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13875,12 +13875,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>46173.67708333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="86">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46173.6875</v>
+        <v>46173.67708333334</v>
       </c>
     </row>
     <row r="87">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14243,10 +14243,10 @@
         <v>2.16</v>
       </c>
       <c r="O87" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="P87" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="O88" t="n">
-        <v>3.13</v>
+        <v>2.77</v>
       </c>
       <c r="P88" t="n">
-        <v>3.05</v>
+        <v>3.63</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.6875</v>
       </c>
     </row>
     <row r="89">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="O91" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="P91" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14988,12 +14988,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>5.3</v>
+        <v>2.19</v>
       </c>
       <c r="O92" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="P92" t="n">
-        <v>1.55</v>
+        <v>3.63</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>46173.72916666666</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="93">
@@ -15147,12 +15147,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15297,7 +15297,7 @@
         <v>0</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>46173.75</v>
+        <v>46173.72916666666</v>
       </c>
     </row>
     <row r="94">
@@ -15306,12 +15306,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="AU94" s="3" t="n">
-        <v>46173.75</v>
+        <v>46173.76041666666</v>
       </c>
     </row>
     <row r="95">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15615,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="AU95" s="3" t="n">
-        <v>46173.76041666666</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="96">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15942,12 +15942,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="AU98" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.83333333334</v>
       </c>
     </row>
     <row r="99">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16260,12 +16260,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.84027777778</v>
       </c>
     </row>
     <row r="101">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="AU101" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.85416666666</v>
       </c>
     </row>
     <row r="102">
@@ -16578,12 +16578,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="O102" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="P102" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="AU102" s="3" t="n">
-        <v>46173.84027777778</v>
+        <v>46173.85416666666</v>
       </c>
     </row>
     <row r="103">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17141,10 +17141,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -17364,165 +17364,6 @@
         <v>0</v>
       </c>
       <c r="AU106" s="3" t="n">
-        <v>46173.85416666666</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Palestino</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP107" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU107" s="3" t="n">
         <v>46173.875</v>
       </c>
     </row>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.55</v>
+        <v>3.46</v>
       </c>
       <c r="O25" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.32</v>
+        <v>2.72</v>
       </c>
       <c r="O35" t="n">
-        <v>5.1</v>
+        <v>2.81</v>
       </c>
       <c r="P35" t="n">
-        <v>8.199999999999999</v>
+        <v>2.81</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>2.81</v>
+        <v>3.31</v>
       </c>
       <c r="P36" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O40" t="n">
-        <v>3.88</v>
+        <v>3.46</v>
       </c>
       <c r="P40" t="n">
-        <v>3.39</v>
+        <v>4.15</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.98</v>
+        <v>1.91</v>
       </c>
       <c r="O41" t="n">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="P41" t="n">
-        <v>2.13</v>
+        <v>3.39</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="O44" t="n">
-        <v>3.46</v>
+        <v>5.99</v>
       </c>
       <c r="P44" t="n">
-        <v>4.15</v>
+        <v>8</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>2.06</v>
+        <v>2.65</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="O53" t="n">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="P53" t="n">
-        <v>4.72</v>
+        <v>5.8</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="O60" t="n">
-        <v>4.35</v>
+        <v>5.45</v>
       </c>
       <c r="P60" t="n">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="O61" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="P61" t="n">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11570,10 +11570,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O71" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="P71" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="O73" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
       <c r="P73" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12047,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.29</v>
+        <v>1.22</v>
       </c>
       <c r="O74" t="n">
-        <v>2.93</v>
+        <v>6.3</v>
       </c>
       <c r="P74" t="n">
-        <v>3.47</v>
+        <v>16</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,64 +12650,64 @@
         </is>
       </c>
       <c r="N77" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O77" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P77" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X77" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y77" t="n">
         <v>1.22</v>
       </c>
-      <c r="O77" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="P77" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12926,22 +12926,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,64 +12968,64 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="AJ79" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL79" t="n">
         <v>0</v>
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,64 +13286,64 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="O81" t="n">
-        <v>4.65</v>
+        <v>3.91</v>
       </c>
       <c r="P81" t="n">
-        <v>7.45</v>
+        <v>3.97</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13356,10 +13356,10 @@
         </is>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL81" t="n">
         <v>0</v>
@@ -13403,22 +13403,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,64 +13445,64 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="O82" t="n">
-        <v>3.91</v>
+        <v>4.65</v>
       </c>
       <c r="P82" t="n">
-        <v>3.97</v>
+        <v>7.45</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB82" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13515,10 +13515,10 @@
         </is>
       </c>
       <c r="AJ82" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13637,10 +13637,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.82</v>
+        <v>2.66</v>
       </c>
       <c r="O84" t="n">
-        <v>3.38</v>
+        <v>2.67</v>
       </c>
       <c r="P84" t="n">
-        <v>4.39</v>
+        <v>2.78</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13802,10 +13802,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="O91" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="P91" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="O92" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="P92" t="n">
-        <v>3.63</v>
+        <v>3.05</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="O104" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="P104" t="n">
-        <v>3.54</v>
+        <v>2.76</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O36" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="P36" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>5.1</v>
+        <v>3.31</v>
       </c>
       <c r="P37" t="n">
-        <v>8.199999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.26</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
-        <v>5.99</v>
+        <v>3.87</v>
       </c>
       <c r="P44" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="P45" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3.23</v>
+        <v>1.83</v>
       </c>
       <c r="O47" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P47" t="n">
-        <v>2.06</v>
+        <v>4.15</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.15</v>
+        <v>3.23</v>
       </c>
       <c r="O49" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P49" t="n">
-        <v>3.13</v>
+        <v>2.06</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.96</v>
+        <v>3.01</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>3.73</v>
       </c>
       <c r="P55" t="n">
-        <v>3.85</v>
+        <v>2.24</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="O56" t="n">
-        <v>3.8</v>
+        <v>5.45</v>
       </c>
       <c r="P56" t="n">
-        <v>4.72</v>
+        <v>7.9</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="O60" t="n">
-        <v>5.45</v>
+        <v>4.35</v>
       </c>
       <c r="P60" t="n">
-        <v>7.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="O61" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="P61" t="n">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>6.34</v>
+        <v>3.59</v>
       </c>
       <c r="O62" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="P62" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.68</v>
+        <v>6.34</v>
       </c>
       <c r="O65" t="n">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="P65" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,14 +11219,14 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="O68" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P68" t="n">
         <v>2.7</v>
       </c>
-      <c r="P68" t="n">
-        <v>2.91</v>
-      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O69" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P69" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,64 +11537,64 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="AJ70" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL70" t="n">
         <v>0</v>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="O71" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="P71" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,64 +11855,64 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.29</v>
+        <v>2.66</v>
       </c>
       <c r="O73" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="P73" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,64 +12650,64 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="O77" t="n">
-        <v>3.63</v>
+        <v>2.64</v>
       </c>
       <c r="P77" t="n">
-        <v>3.93</v>
+        <v>3.55</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="Z77" t="n">
-        <v>3.8</v>
+        <v>1.97</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="AJ77" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK77" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="O80" t="n">
-        <v>3.37</v>
+        <v>4.65</v>
       </c>
       <c r="P80" t="n">
-        <v>3.44</v>
+        <v>7.45</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13244,22 +13244,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,64 +13286,64 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="O81" t="n">
-        <v>3.91</v>
+        <v>2.93</v>
       </c>
       <c r="P81" t="n">
-        <v>3.97</v>
+        <v>3.47</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13356,10 +13356,10 @@
         </is>
       </c>
       <c r="AJ81" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>7.45</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13484,10 +13484,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13637,10 +13637,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="O84" t="n">
-        <v>2.67</v>
+        <v>3.37</v>
       </c>
       <c r="P84" t="n">
-        <v>2.78</v>
+        <v>3.44</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="O90" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="P90" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="O91" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="P91" t="n">
-        <v>3.63</v>
+        <v>3.05</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O103" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P103" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -16982,10 +16982,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O23" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O37" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="P37" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,22 +6566,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="O42" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P42" t="n">
-        <v>3.13</v>
+        <v>4.15</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="O44" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="P44" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.83</v>
+        <v>2.81</v>
       </c>
       <c r="O47" t="n">
-        <v>3.46</v>
+        <v>3.85</v>
       </c>
       <c r="P47" t="n">
-        <v>4.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="O49" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>2.06</v>
+        <v>2.65</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>3.87</v>
       </c>
       <c r="P51" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.01</v>
+        <v>2.43</v>
       </c>
       <c r="O55" t="n">
-        <v>3.73</v>
+        <v>3.31</v>
       </c>
       <c r="P55" t="n">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="O58" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="P58" t="n">
-        <v>3.85</v>
+        <v>3.12</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="O59" t="n">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="P59" t="n">
-        <v>4.72</v>
+        <v>5.8</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="O60" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.8</v>
+        <v>4.72</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="O61" t="n">
-        <v>3.33</v>
+        <v>5.45</v>
       </c>
       <c r="P61" t="n">
-        <v>3.12</v>
+        <v>7.9</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.59</v>
+        <v>2.68</v>
       </c>
       <c r="O62" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P62" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.61</v>
+        <v>3.59</v>
       </c>
       <c r="O63" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P63" t="n">
-        <v>4.3</v>
+        <v>1.83</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10469,10 +10469,10 @@
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.68</v>
+        <v>6.34</v>
       </c>
       <c r="O64" t="n">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="P64" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>6.34</v>
+        <v>1.61</v>
       </c>
       <c r="O65" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P65" t="n">
-        <v>1.41</v>
+        <v>4.3</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="O66" t="n">
         <v>3.3</v>
       </c>
       <c r="P66" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="O67" t="n">
         <v>3.3</v>
       </c>
       <c r="P67" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,64 +11537,64 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O70" t="n">
-        <v>3.91</v>
+        <v>3.2</v>
       </c>
       <c r="P70" t="n">
-        <v>3.97</v>
+        <v>4.33</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="AJ70" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL70" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,64 +11855,64 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="AJ72" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL72" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,64 +12014,64 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="O73" t="n">
-        <v>2.67</v>
+        <v>3.63</v>
       </c>
       <c r="P73" t="n">
-        <v>2.78</v>
+        <v>3.93</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL73" t="n">
         <v>0</v>
@@ -12131,22 +12131,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,64 +12173,64 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12243,10 +12243,10 @@
         </is>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1.82</v>
+        <v>1.22</v>
       </c>
       <c r="O75" t="n">
-        <v>3.38</v>
+        <v>6.3</v>
       </c>
       <c r="P75" t="n">
-        <v>4.39</v>
+        <v>16</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="O76" t="n">
-        <v>2.68</v>
+        <v>3.37</v>
       </c>
       <c r="P76" t="n">
-        <v>2.68</v>
+        <v>3.44</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.28</v>
+        <v>1.27</v>
       </c>
       <c r="O77" t="n">
-        <v>2.64</v>
+        <v>4.65</v>
       </c>
       <c r="P77" t="n">
-        <v>3.55</v>
+        <v>7.45</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12683,16 +12683,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.22</v>
+        <v>1.82</v>
       </c>
       <c r="O79" t="n">
-        <v>6.3</v>
+        <v>3.38</v>
       </c>
       <c r="P79" t="n">
-        <v>16</v>
+        <v>4.39</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1.27</v>
+        <v>2.29</v>
       </c>
       <c r="O80" t="n">
-        <v>4.65</v>
+        <v>2.93</v>
       </c>
       <c r="P80" t="n">
-        <v>7.45</v>
+        <v>3.47</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.29</v>
+        <v>2.66</v>
       </c>
       <c r="O81" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="P81" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13478,10 +13478,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="O84" t="n">
-        <v>3.37</v>
+        <v>2.64</v>
       </c>
       <c r="P84" t="n">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13796,10 +13796,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="O89" t="n">
-        <v>2.86</v>
+        <v>3.13</v>
       </c>
       <c r="P89" t="n">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="O91" t="n">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="P91" t="n">
-        <v>3.05</v>
+        <v>3.56</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>3.19</v>
+        <v>2.64</v>
       </c>
       <c r="O101" t="n">
-        <v>3.29</v>
+        <v>2.96</v>
       </c>
       <c r="P101" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="O102" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16664,10 +16664,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2.15</v>
+        <v>3.19</v>
       </c>
       <c r="O103" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="P103" t="n">
-        <v>3.54</v>
+        <v>2.36</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P24" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5180,10 +5180,10 @@
         <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5975,10 +5975,10 @@
         <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.26</v>
+        <v>2.15</v>
       </c>
       <c r="O39" t="n">
-        <v>5.99</v>
+        <v>3.35</v>
       </c>
       <c r="P39" t="n">
-        <v>8</v>
+        <v>3.13</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O42" t="n">
-        <v>3.46</v>
+        <v>3.88</v>
       </c>
       <c r="P42" t="n">
-        <v>4.15</v>
+        <v>3.39</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>2.06</v>
+        <v>2.65</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.65</v>
+        <v>1.26</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>5.99</v>
       </c>
       <c r="P49" t="n">
-        <v>2.65</v>
+        <v>8</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3.8</v>
+        <v>1.83</v>
       </c>
       <c r="O51" t="n">
-        <v>3.87</v>
+        <v>3.46</v>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>4.15</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.96</v>
+        <v>2.43</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="P54" t="n">
-        <v>3.85</v>
+        <v>2.84</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.43</v>
+        <v>1.3</v>
       </c>
       <c r="O55" t="n">
-        <v>3.31</v>
+        <v>5.45</v>
       </c>
       <c r="P55" t="n">
-        <v>2.84</v>
+        <v>7.9</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O58" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="P58" t="n">
-        <v>3.12</v>
+        <v>4.72</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="O60" t="n">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="P60" t="n">
-        <v>4.72</v>
+        <v>5.8</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="O61" t="n">
-        <v>5.45</v>
+        <v>3.33</v>
       </c>
       <c r="P61" t="n">
-        <v>7.9</v>
+        <v>3.12</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.68</v>
+        <v>1.61</v>
       </c>
       <c r="O62" t="n">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="P62" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>3.59</v>
+        <v>6.34</v>
       </c>
       <c r="O63" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="P63" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10469,10 +10469,10 @@
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>6.34</v>
+        <v>3.59</v>
       </c>
       <c r="O64" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="P64" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10628,10 +10628,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.61</v>
+        <v>2.68</v>
       </c>
       <c r="O65" t="n">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="P65" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O70" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="P70" t="n">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="O71" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="P71" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,64 +12014,64 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.85</v>
+        <v>2.29</v>
       </c>
       <c r="O73" t="n">
-        <v>3.63</v>
+        <v>2.93</v>
       </c>
       <c r="P73" t="n">
-        <v>3.93</v>
+        <v>3.47</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="AJ73" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL73" t="n">
         <v>0</v>
@@ -12131,22 +12131,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,64 +12173,64 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O74" t="n">
-        <v>3.91</v>
+        <v>3.2</v>
       </c>
       <c r="P74" t="n">
-        <v>3.97</v>
+        <v>4.2</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12243,10 +12243,10 @@
         </is>
       </c>
       <c r="AJ74" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="O75" t="n">
-        <v>6.3</v>
+        <v>4.65</v>
       </c>
       <c r="P75" t="n">
-        <v>16</v>
+        <v>7.45</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="O76" t="n">
-        <v>3.37</v>
+        <v>6.3</v>
       </c>
       <c r="P76" t="n">
-        <v>3.44</v>
+        <v>16</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="O77" t="n">
-        <v>4.65</v>
+        <v>3.37</v>
       </c>
       <c r="P77" t="n">
-        <v>7.45</v>
+        <v>3.44</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="O78" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="P78" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13007,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.29</v>
+        <v>2.66</v>
       </c>
       <c r="O80" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="P80" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="O83" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="P83" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13637,10 +13637,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -13721,22 +13721,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,64 +13763,64 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.28</v>
+        <v>1.78</v>
       </c>
       <c r="O84" t="n">
-        <v>2.64</v>
+        <v>3.91</v>
       </c>
       <c r="P84" t="n">
-        <v>3.55</v>
+        <v>3.97</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.72</v>
+        <v>1.19</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.97</v>
+        <v>4.95</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -13833,10 +13833,10 @@
         </is>
       </c>
       <c r="AJ84" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK84" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL84" t="n">
         <v>0</v>
@@ -13880,22 +13880,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,64 +13922,64 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -13992,10 +13992,10 @@
         </is>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK85" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL85" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="O89" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="P89" t="n">
-        <v>3.05</v>
+        <v>3.63</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="O90" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="P90" t="n">
-        <v>3.63</v>
+        <v>3.05</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.55</v>
+        <v>3.19</v>
       </c>
       <c r="O102" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="P102" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>3.19</v>
+        <v>2.55</v>
       </c>
       <c r="O103" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="P103" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="O105" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="P105" t="n">
-        <v>3.54</v>
+        <v>2.76</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17141,10 +17141,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.07</v>
+        <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>3.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>3.46</v>
       </c>
       <c r="O24" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O30" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="P30" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="P35" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>2.81</v>
+        <v>3.31</v>
       </c>
       <c r="P37" t="n">
-        <v>2.81</v>
+        <v>3.27</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.15</v>
+        <v>1.26</v>
       </c>
       <c r="O39" t="n">
-        <v>3.35</v>
+        <v>5.99</v>
       </c>
       <c r="P39" t="n">
-        <v>3.13</v>
+        <v>8</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,22 +6725,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,22 +7679,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.26</v>
+        <v>3.23</v>
       </c>
       <c r="O49" t="n">
-        <v>5.99</v>
+        <v>3.5</v>
       </c>
       <c r="P49" t="n">
-        <v>8</v>
+        <v>2.06</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>3.23</v>
+        <v>1.83</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P50" t="n">
-        <v>2.06</v>
+        <v>4.15</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.83</v>
+        <v>2.98</v>
       </c>
       <c r="O51" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="P51" t="n">
-        <v>4.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="O55" t="n">
-        <v>5.45</v>
+        <v>3.33</v>
       </c>
       <c r="P55" t="n">
-        <v>7.9</v>
+        <v>3.12</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>3.01</v>
+        <v>1.96</v>
       </c>
       <c r="O56" t="n">
-        <v>3.73</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="O57" t="n">
-        <v>3.34</v>
+        <v>5.45</v>
       </c>
       <c r="P57" t="n">
-        <v>3.85</v>
+        <v>7.9</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O61" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="P61" t="n">
-        <v>3.12</v>
+        <v>4.72</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.61</v>
+        <v>2.68</v>
       </c>
       <c r="O62" t="n">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="P62" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3.59</v>
+        <v>1.61</v>
       </c>
       <c r="O64" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="P64" t="n">
-        <v>1.83</v>
+        <v>4.3</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10628,10 +10628,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.68</v>
+        <v>3.59</v>
       </c>
       <c r="O65" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P65" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10787,10 +10787,10 @@
         <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="O66" t="n">
         <v>3.3</v>
       </c>
       <c r="P66" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="O67" t="n">
         <v>3.3</v>
       </c>
       <c r="P67" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O68" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P68" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,14 +11378,14 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P69" t="n">
         <v>2.7</v>
       </c>
-      <c r="P69" t="n">
-        <v>2.91</v>
-      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="O70" t="n">
-        <v>3.38</v>
+        <v>4.65</v>
       </c>
       <c r="P70" t="n">
-        <v>4.39</v>
+        <v>7.45</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,64 +11855,64 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>3.91</v>
       </c>
       <c r="P72" t="n">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL72" t="n">
         <v>0</v>
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="O73" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="P73" t="n">
-        <v>3.47</v>
+        <v>4.39</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="O74" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="P74" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1.27</v>
+        <v>2.66</v>
       </c>
       <c r="O75" t="n">
-        <v>4.65</v>
+        <v>2.67</v>
       </c>
       <c r="P75" t="n">
-        <v>7.45</v>
+        <v>2.78</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="O76" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="P76" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,65 +12650,65 @@
         </is>
       </c>
       <c r="N77" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O77" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P77" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X77" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG77" t="n">
         <v>2.2</v>
       </c>
-      <c r="O77" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="P77" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>0</v>
-      </c>
       <c r="AH77" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="O78" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="P78" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="O80" t="n">
-        <v>2.67</v>
+        <v>3.37</v>
       </c>
       <c r="P80" t="n">
-        <v>2.78</v>
+        <v>3.44</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13721,22 +13721,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,64 +13763,64 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -13833,10 +13833,10 @@
         </is>
       </c>
       <c r="AJ84" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK84" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL84" t="n">
         <v>0</v>
@@ -13880,22 +13880,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,64 +13922,64 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="O85" t="n">
-        <v>3.63</v>
+        <v>6.3</v>
       </c>
       <c r="P85" t="n">
-        <v>3.93</v>
+        <v>16</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -13992,10 +13992,10 @@
         </is>
       </c>
       <c r="AJ85" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL85" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14243,10 +14243,10 @@
         <v>2.16</v>
       </c>
       <c r="O87" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="P87" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14402,10 +14402,10 @@
         <v>2.16</v>
       </c>
       <c r="O88" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="P88" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="O89" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="P89" t="n">
-        <v>3.63</v>
+        <v>3.05</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="O91" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="P91" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>3.19</v>
+        <v>2.55</v>
       </c>
       <c r="O102" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="P102" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="O103" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P103" t="n">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16823,10 +16823,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.15</v>
+        <v>3.19</v>
       </c>
       <c r="O104" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="P104" t="n">
-        <v>3.54</v>
+        <v>2.36</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="O105" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="P105" t="n">
-        <v>2.76</v>
+        <v>3.54</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -17141,10 +17141,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>3.33</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.46</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6293,10 +6293,10 @@
         <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.26</v>
+        <v>2.98</v>
       </c>
       <c r="O39" t="n">
-        <v>5.99</v>
+        <v>3.72</v>
       </c>
       <c r="P39" t="n">
-        <v>8</v>
+        <v>2.13</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>3.23</v>
       </c>
       <c r="O40" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P40" t="n">
-        <v>3.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>3.87</v>
       </c>
       <c r="P43" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.81</v>
+        <v>1.91</v>
       </c>
       <c r="O46" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>3.39</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="O51" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="P51" t="n">
-        <v>2.13</v>
+        <v>3.13</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="O60" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.8</v>
+        <v>4.72</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="O61" t="n">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="P61" t="n">
-        <v>4.72</v>
+        <v>5.8</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.68</v>
+        <v>3.59</v>
       </c>
       <c r="O62" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P62" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>6.34</v>
+        <v>2.68</v>
       </c>
       <c r="O63" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="P63" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.61</v>
+        <v>6.34</v>
       </c>
       <c r="O64" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.3</v>
+        <v>1.41</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3.59</v>
+        <v>1.61</v>
       </c>
       <c r="O65" t="n">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="P65" t="n">
-        <v>1.83</v>
+        <v>4.3</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10787,10 +10787,10 @@
         <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="O66" t="n">
         <v>3.3</v>
       </c>
       <c r="P66" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="O67" t="n">
         <v>3.3</v>
       </c>
       <c r="P67" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,14 +11219,14 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="O68" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P68" t="n">
         <v>2.7</v>
       </c>
-      <c r="P68" t="n">
-        <v>2.91</v>
-      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O69" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P69" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.27</v>
+        <v>2.46</v>
       </c>
       <c r="O70" t="n">
-        <v>4.65</v>
+        <v>2.74</v>
       </c>
       <c r="P70" t="n">
-        <v>7.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,64 +11855,64 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.78</v>
+        <v>2.66</v>
       </c>
       <c r="O72" t="n">
-        <v>3.91</v>
+        <v>2.67</v>
       </c>
       <c r="P72" t="n">
-        <v>3.97</v>
+        <v>2.78</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="AJ72" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="O73" t="n">
-        <v>3.38</v>
+        <v>2.64</v>
       </c>
       <c r="P73" t="n">
-        <v>4.39</v>
+        <v>3.55</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12047,16 +12047,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,13 +12173,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="O74" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="P74" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.66</v>
+        <v>2.29</v>
       </c>
       <c r="O75" t="n">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="P75" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O76" t="n">
         <v>3.2</v>
       </c>
       <c r="P76" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12608,22 +12608,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,64 +12650,64 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="O77" t="n">
-        <v>3.63</v>
+        <v>4.65</v>
       </c>
       <c r="P77" t="n">
-        <v>3.93</v>
+        <v>7.45</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AB77" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="AJ77" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK77" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL77" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="O78" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="P78" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -12926,22 +12926,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,64 +12968,64 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O79" t="n">
-        <v>3.2</v>
+        <v>3.91</v>
       </c>
       <c r="P79" t="n">
-        <v>4.33</v>
+        <v>3.97</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="AJ79" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK79" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL79" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13478,10 +13478,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -13562,22 +13562,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,64 +13604,64 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="O83" t="n">
-        <v>2.64</v>
+        <v>3.63</v>
       </c>
       <c r="P83" t="n">
-        <v>3.55</v>
+        <v>3.93</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.97</v>
+        <v>3.8</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL83" t="n">
         <v>0</v>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.22</v>
+        <v>1.82</v>
       </c>
       <c r="O85" t="n">
-        <v>6.3</v>
+        <v>3.38</v>
       </c>
       <c r="P85" t="n">
-        <v>16</v>
+        <v>4.39</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13961,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14243,10 +14243,10 @@
         <v>2.16</v>
       </c>
       <c r="O87" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="P87" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14402,10 +14402,10 @@
         <v>2.16</v>
       </c>
       <c r="O88" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="P88" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2.64</v>
+        <v>3.19</v>
       </c>
       <c r="O103" t="n">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="P103" t="n">
-        <v>2.76</v>
+        <v>2.36</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16823,10 +16823,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O104" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P104" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O22" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P22" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="O31" t="n">
-        <v>3.31</v>
+        <v>5.1</v>
       </c>
       <c r="P31" t="n">
-        <v>3.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>8.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.98</v>
+        <v>3.23</v>
       </c>
       <c r="O39" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="O40" t="n">
-        <v>3.5</v>
+        <v>3.87</v>
       </c>
       <c r="P40" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.91</v>
+        <v>2.81</v>
       </c>
       <c r="O46" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="P46" t="n">
-        <v>3.39</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,22 +7838,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.65</v>
+        <v>1.26</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>5.99</v>
       </c>
       <c r="P47" t="n">
-        <v>2.65</v>
+        <v>8</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.81</v>
+        <v>2.15</v>
       </c>
       <c r="O48" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="P48" t="n">
-        <v>2.19</v>
+        <v>3.13</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.83</v>
+        <v>2.98</v>
       </c>
       <c r="O50" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="P50" t="n">
-        <v>4.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O51" t="n">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
       <c r="P51" t="n">
-        <v>3.13</v>
+        <v>3.39</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>3.01</v>
+        <v>2.25</v>
       </c>
       <c r="O54" t="n">
-        <v>3.73</v>
+        <v>3.33</v>
       </c>
       <c r="P54" t="n">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="O57" t="n">
-        <v>5.45</v>
+        <v>3.8</v>
       </c>
       <c r="P57" t="n">
-        <v>7.9</v>
+        <v>4.72</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="O58" t="n">
-        <v>3.34</v>
+        <v>4.35</v>
       </c>
       <c r="P58" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.43</v>
+        <v>1.96</v>
       </c>
       <c r="O59" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="P59" t="n">
-        <v>2.84</v>
+        <v>3.85</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.68</v>
+        <v>3.01</v>
       </c>
       <c r="O60" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="P60" t="n">
-        <v>4.72</v>
+        <v>2.24</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3.59</v>
+        <v>6.34</v>
       </c>
       <c r="O62" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="P62" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.68</v>
+        <v>1.61</v>
       </c>
       <c r="O63" t="n">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="P63" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>6.34</v>
+        <v>3.59</v>
       </c>
       <c r="O64" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="P64" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10628,10 +10628,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.61</v>
+        <v>2.68</v>
       </c>
       <c r="O65" t="n">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="P65" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="O66" t="n">
         <v>3.3</v>
       </c>
       <c r="P66" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="O67" t="n">
         <v>3.3</v>
       </c>
       <c r="P67" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O68" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="P68" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,14 +11378,14 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P69" t="n">
         <v>2.7</v>
       </c>
-      <c r="P69" t="n">
-        <v>2.91</v>
-      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2.46</v>
+        <v>1.27</v>
       </c>
       <c r="O70" t="n">
-        <v>2.74</v>
+        <v>4.65</v>
       </c>
       <c r="P70" t="n">
-        <v>3.05</v>
+        <v>7.45</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.76</v>
+        <v>1.8</v>
       </c>
       <c r="O71" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="P71" t="n">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11729,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,13 +12014,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="O73" t="n">
-        <v>2.64</v>
+        <v>3.38</v>
       </c>
       <c r="P73" t="n">
-        <v>3.55</v>
+        <v>4.39</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -12047,16 +12047,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -12131,22 +12131,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,64 +12173,64 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O74" t="n">
-        <v>3.2</v>
+        <v>3.63</v>
       </c>
       <c r="P74" t="n">
-        <v>4.2</v>
+        <v>3.93</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12243,10 +12243,10 @@
         </is>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="O76" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P76" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.27</v>
+        <v>2.29</v>
       </c>
       <c r="O77" t="n">
-        <v>4.65</v>
+        <v>2.93</v>
       </c>
       <c r="P77" t="n">
-        <v>7.45</v>
+        <v>3.47</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12777,12 +12777,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="O78" t="n">
-        <v>6.3</v>
+        <v>3.37</v>
       </c>
       <c r="P78" t="n">
-        <v>16</v>
+        <v>3.44</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="O80" t="n">
-        <v>3.37</v>
+        <v>2.74</v>
       </c>
       <c r="P80" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13562,22 +13562,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,64 +13604,64 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="O83" t="n">
-        <v>3.63</v>
+        <v>2.64</v>
       </c>
       <c r="P83" t="n">
-        <v>3.93</v>
+        <v>3.55</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="Z83" t="n">
-        <v>3.8</v>
+        <v>1.97</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13674,10 +13674,10 @@
         </is>
       </c>
       <c r="AJ83" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL83" t="n">
         <v>0</v>
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="O84" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P84" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1.82</v>
+        <v>2.76</v>
       </c>
       <c r="O85" t="n">
-        <v>3.38</v>
+        <v>2.68</v>
       </c>
       <c r="P85" t="n">
-        <v>4.39</v>
+        <v>2.68</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13955,16 +13955,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O103" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P103" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -16911,12 +16911,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16943,13 +16943,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>2.15</v>
+        <v>3.19</v>
       </c>
       <c r="O104" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="P104" t="n">
-        <v>3.54</v>
+        <v>2.36</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -17102,13 +17102,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU106"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.07</v>
+        <v>3.16</v>
       </c>
       <c r="O4" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>3.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="P34" t="n">
-        <v>3.27</v>
+        <v>2.81</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5975,10 +5975,10 @@
         <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="P35" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.72</v>
+        <v>1.32</v>
       </c>
       <c r="O37" t="n">
-        <v>2.81</v>
+        <v>5.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2.81</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3.23</v>
+        <v>1.91</v>
       </c>
       <c r="O39" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>3.39</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="O40" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,22 +6884,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,22 +7202,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,22 +7361,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.65</v>
+        <v>1.26</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>5.99</v>
       </c>
       <c r="P44" t="n">
-        <v>2.65</v>
+        <v>8</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,22 +7520,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.81</v>
+        <v>2.15</v>
       </c>
       <c r="O46" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>3.13</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7833,27 +7833,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.26</v>
+        <v>3.01</v>
       </c>
       <c r="O47" t="n">
-        <v>5.99</v>
+        <v>3.73</v>
       </c>
       <c r="P47" t="n">
-        <v>8</v>
+        <v>2.24</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46173.5</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="48">
@@ -7992,27 +7992,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="O48" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="P48" t="n">
-        <v>3.13</v>
+        <v>3.85</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46173.5</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="49">
@@ -8151,27 +8151,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.83</v>
+        <v>1.49</v>
       </c>
       <c r="O49" t="n">
-        <v>3.46</v>
+        <v>4.35</v>
       </c>
       <c r="P49" t="n">
-        <v>4.15</v>
+        <v>5.8</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>46173.5</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="50">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46173.5</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="51">
@@ -8469,27 +8469,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="O51" t="n">
-        <v>3.88</v>
+        <v>3.33</v>
       </c>
       <c r="P51" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46173.5</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="52">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>46173.54166666666</v>
+        <v>46173.5625</v>
       </c>
     </row>
     <row r="53">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O54" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="P54" t="n">
-        <v>3.12</v>
+        <v>4.72</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9264,27 +9264,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.43</v>
+        <v>1.79</v>
       </c>
       <c r="O56" t="n">
-        <v>3.31</v>
+        <v>2.95</v>
       </c>
       <c r="P56" t="n">
-        <v>2.84</v>
+        <v>4.96</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.88</v>
+        <v>2.74</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -9423,27 +9423,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="O57" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="P57" t="n">
-        <v>4.72</v>
+        <v>4.3</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="58">
@@ -9582,27 +9582,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.49</v>
+        <v>2.68</v>
       </c>
       <c r="O58" t="n">
-        <v>4.35</v>
+        <v>3.68</v>
       </c>
       <c r="P58" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -9741,27 +9741,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.96</v>
+        <v>6.34</v>
       </c>
       <c r="O59" t="n">
-        <v>3.34</v>
+        <v>4.5</v>
       </c>
       <c r="P59" t="n">
-        <v>3.85</v>
+        <v>1.41</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="60">
@@ -9900,27 +9900,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>3.01</v>
+        <v>3.59</v>
       </c>
       <c r="O60" t="n">
-        <v>3.73</v>
+        <v>4.05</v>
       </c>
       <c r="P60" t="n">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46173.5625</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="62">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>6.34</v>
+        <v>2.25</v>
       </c>
       <c r="O62" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P62" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="63">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="O63" t="n">
-        <v>4.55</v>
+        <v>3.55</v>
       </c>
       <c r="P63" t="n">
-        <v>4.3</v>
+        <v>6.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="64">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3.59</v>
+        <v>2.52</v>
       </c>
       <c r="O64" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="P64" t="n">
-        <v>1.83</v>
+        <v>2.91</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10628,10 +10628,10 @@
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.64583333334</v>
       </c>
     </row>
     <row r="65">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.68</v>
+        <v>1.27</v>
       </c>
       <c r="O65" t="n">
-        <v>3.68</v>
+        <v>4.65</v>
       </c>
       <c r="P65" t="n">
-        <v>2.3</v>
+        <v>7.45</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46173.58333333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="66">
@@ -10854,12 +10854,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="O66" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="P66" t="n">
-        <v>2.8</v>
+        <v>3.47</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46173.625</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="67">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O67" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P67" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46173.625</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="68">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>46173.64583333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="69">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="O69" t="n">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -11411,10 +11411,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AU69" s="3" t="n">
-        <v>46173.64583333334</v>
+        <v>46173.66666666666</v>
       </c>
     </row>
     <row r="70">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,13 +11537,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="O70" t="n">
-        <v>4.65</v>
+        <v>6.3</v>
       </c>
       <c r="P70" t="n">
-        <v>7.45</v>
+        <v>16</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,64 +11855,64 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL72" t="n">
         <v>0</v>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,64 +12014,64 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="O73" t="n">
-        <v>3.38</v>
+        <v>2.74</v>
       </c>
       <c r="P73" t="n">
-        <v>4.39</v>
+        <v>3.69</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL73" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12365,10 +12365,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1.91</v>
+        <v>2.76</v>
       </c>
       <c r="O76" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="P76" t="n">
-        <v>3.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="O77" t="n">
-        <v>2.93</v>
+        <v>3.38</v>
       </c>
       <c r="P77" t="n">
-        <v>3.47</v>
+        <v>4.39</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12926,22 +12926,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,64 +12968,64 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O79" t="n">
-        <v>3.91</v>
+        <v>3.2</v>
       </c>
       <c r="P79" t="n">
-        <v>3.97</v>
+        <v>4.33</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="AJ79" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL79" t="n">
         <v>0</v>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="O80" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="P80" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1.22</v>
+        <v>2.46</v>
       </c>
       <c r="O81" t="n">
-        <v>6.3</v>
+        <v>2.74</v>
       </c>
       <c r="P81" t="n">
-        <v>16</v>
+        <v>3.05</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13398,12 +13398,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2.66</v>
+        <v>5.77</v>
       </c>
       <c r="O82" t="n">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="P82" t="n">
-        <v>2.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.67708333334</v>
       </c>
     </row>
     <row r="83">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="O83" t="n">
-        <v>2.64</v>
+        <v>2.77</v>
       </c>
       <c r="P83" t="n">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13637,10 +13637,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.6875</v>
       </c>
     </row>
     <row r="84">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="O84" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="P84" t="n">
-        <v>4.33</v>
+        <v>3.63</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13866,7 +13866,7 @@
         <v>0</v>
       </c>
       <c r="AU84" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="85">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.76</v>
+        <v>2.13</v>
       </c>
       <c r="O85" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="P85" t="n">
-        <v>2.68</v>
+        <v>3.56</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -13955,10 +13955,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -14025,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="AU85" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="86">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>5.77</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="AU86" s="3" t="n">
-        <v>46173.67708333334</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="87">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="O87" t="n">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="P87" t="n">
-        <v>3.69</v>
+        <v>3.05</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>46173.6875</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="88">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2.16</v>
+        <v>5.3</v>
       </c>
       <c r="O88" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="P88" t="n">
-        <v>3.63</v>
+        <v>1.55</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>46173.6875</v>
+        <v>46173.72916666666</v>
       </c>
     </row>
     <row r="89">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.76041666666</v>
       </c>
     </row>
     <row r="90">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>0</v>
       </c>
       <c r="AU90" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="91">
@@ -14829,12 +14829,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="AU91" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="92">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="93">
@@ -15147,12 +15147,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="O93" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="P93" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15236,7 +15236,7 @@
         <v>1.94</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15297,7 +15297,7 @@
         <v>0</v>
       </c>
       <c r="AU93" s="3" t="n">
-        <v>46173.72916666666</v>
+        <v>46173.83333333334</v>
       </c>
     </row>
     <row r="94">
@@ -15306,12 +15306,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="AU94" s="3" t="n">
-        <v>46173.76041666666</v>
+        <v>46173.83333333334</v>
       </c>
     </row>
     <row r="95">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="O95" t="n">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="P95" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15615,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="AU95" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.84027777778</v>
       </c>
     </row>
     <row r="96">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="AU96" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.85416666666</v>
       </c>
     </row>
     <row r="97">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="AU97" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.85416666666</v>
       </c>
     </row>
     <row r="98">
@@ -15942,12 +15942,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="O98" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="P98" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16092,7 +16092,7 @@
         <v>0</v>
       </c>
       <c r="AU98" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.85416666666</v>
       </c>
     </row>
     <row r="99">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16251,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="AU99" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.85416666666</v>
       </c>
     </row>
     <row r="100">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="O100" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="P100" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16346,10 +16346,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46173.84027777778</v>
+        <v>46173.85416666666</v>
       </c>
     </row>
     <row r="101">
@@ -16419,12 +16419,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -16466,13 +16466,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -16505,10 +16505,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -16569,801 +16569,6 @@
         <v>0</v>
       </c>
       <c r="AU101" s="3" t="n">
-        <v>46173.85416666666</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Blooming</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO102" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP102" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU102" s="3" t="n">
-        <v>46173.85416666666</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N103" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O103" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P103" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM103" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN103" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO103" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP103" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU103" s="3" t="n">
-        <v>46173.85416666666</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Remo</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N104" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="O104" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="P104" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM104" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN104" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO104" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP104" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU104" s="3" t="n">
-        <v>46173.85416666666</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Figueirense</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Paysandu</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N105" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O105" t="n">
-        <v>3</v>
-      </c>
-      <c r="P105" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM105" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN105" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO105" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP105" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU105" s="3" t="n">
-        <v>46173.85416666666</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Palestino</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM106" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN106" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO106" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP106" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU106" s="3" t="n">
         <v>46173.875</v>
       </c>
     </row>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU101"/>
+  <dimension ref="A1:AU100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.07</v>
+        <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>3.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="O23" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>8.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.91</v>
+        <v>3.23</v>
       </c>
       <c r="O39" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P39" t="n">
-        <v>3.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O41" t="n">
-        <v>3.87</v>
+        <v>3.35</v>
       </c>
       <c r="P41" t="n">
-        <v>1.8</v>
+        <v>3.13</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.81</v>
+        <v>1.91</v>
       </c>
       <c r="O42" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="P42" t="n">
-        <v>2.19</v>
+        <v>3.39</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.23</v>
+        <v>2.81</v>
       </c>
       <c r="O43" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P43" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.26</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
-        <v>5.99</v>
+        <v>3.87</v>
       </c>
       <c r="P44" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="O45" t="n">
-        <v>3.46</v>
+        <v>5.99</v>
       </c>
       <c r="P45" t="n">
-        <v>4.15</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="O46" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P46" t="n">
-        <v>3.13</v>
+        <v>4.15</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3.01</v>
+        <v>2.25</v>
       </c>
       <c r="O47" t="n">
-        <v>3.73</v>
+        <v>3.33</v>
       </c>
       <c r="P47" t="n">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="O48" t="n">
-        <v>3.34</v>
+        <v>5.45</v>
       </c>
       <c r="P48" t="n">
-        <v>3.85</v>
+        <v>7.9</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.49</v>
+        <v>2.43</v>
       </c>
       <c r="O49" t="n">
-        <v>4.35</v>
+        <v>3.31</v>
       </c>
       <c r="P49" t="n">
-        <v>5.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="O53" t="n">
-        <v>5.45</v>
+        <v>3.8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.9</v>
+        <v>4.72</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.43</v>
+        <v>3.01</v>
       </c>
       <c r="O55" t="n">
-        <v>3.31</v>
+        <v>3.73</v>
       </c>
       <c r="P55" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.61</v>
+        <v>3.59</v>
       </c>
       <c r="O57" t="n">
-        <v>4.55</v>
+        <v>4.05</v>
       </c>
       <c r="P57" t="n">
-        <v>4.3</v>
+        <v>1.83</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9515,10 +9515,10 @@
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.68</v>
+        <v>1.61</v>
       </c>
       <c r="O58" t="n">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="P58" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>6.34</v>
+        <v>2.68</v>
       </c>
       <c r="O59" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="P59" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>3.59</v>
+        <v>6.34</v>
       </c>
       <c r="O60" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="P60" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="O61" t="n">
         <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,64 +10265,64 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="O62" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P62" t="n">
-        <v>2.75</v>
+        <v>6.55</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.5</v>
+        <v>2.44</v>
       </c>
       <c r="O63" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P63" t="n">
-        <v>6.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="O65" t="n">
-        <v>4.65</v>
+        <v>3.38</v>
       </c>
       <c r="P65" t="n">
-        <v>7.45</v>
+        <v>4.39</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="O66" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>3.47</v>
+        <v>3.7</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,64 +11378,64 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O69" t="n">
-        <v>3</v>
+        <v>3.63</v>
       </c>
       <c r="P69" t="n">
-        <v>3.7</v>
+        <v>3.93</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11448,10 +11448,10 @@
         </is>
       </c>
       <c r="AJ69" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL69" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -11813,22 +11813,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,64 +11855,64 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1.78</v>
+        <v>2.76</v>
       </c>
       <c r="O72" t="n">
-        <v>3.91</v>
+        <v>2.68</v>
       </c>
       <c r="P72" t="n">
-        <v>3.97</v>
+        <v>2.68</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.19</v>
+        <v>1.75</v>
       </c>
       <c r="Z72" t="n">
-        <v>4.95</v>
+        <v>1.93</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -11925,10 +11925,10 @@
         </is>
       </c>
       <c r="AJ72" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL72" t="n">
         <v>0</v>
@@ -11982,12 +11982,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,64 +12014,64 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="O73" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="P73" t="n">
-        <v>3.69</v>
+        <v>2.78</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="AJ73" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL73" t="n">
         <v>0</v>
@@ -12131,22 +12131,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,64 +12173,64 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="O74" t="n">
-        <v>3.63</v>
+        <v>2.74</v>
       </c>
       <c r="P74" t="n">
-        <v>3.93</v>
+        <v>3.69</v>
       </c>
       <c r="Q74" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U74" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF74" t="n">
         <v>2.45</v>
       </c>
-      <c r="R74" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S74" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T74" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U74" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V74" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X74" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG74" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12243,10 +12243,10 @@
         </is>
       </c>
       <c r="AJ74" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK74" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AL74" t="n">
         <v>0</v>
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="O75" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="P75" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12365,10 +12365,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12524,10 +12524,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="O77" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="P77" t="n">
-        <v>4.39</v>
+        <v>3.44</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12689,10 +12689,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -12767,22 +12767,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,64 +12809,64 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="O78" t="n">
-        <v>3.37</v>
+        <v>3.91</v>
       </c>
       <c r="P78" t="n">
-        <v>3.44</v>
+        <v>3.97</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2.66</v>
+        <v>1.75</v>
       </c>
       <c r="O80" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="P80" t="n">
-        <v>2.78</v>
+        <v>4.33</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13239,12 +13239,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2.46</v>
+        <v>5.77</v>
       </c>
       <c r="O81" t="n">
-        <v>2.74</v>
+        <v>4.8</v>
       </c>
       <c r="P81" t="n">
-        <v>3.05</v>
+        <v>1.47</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -13389,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="AU81" s="3" t="n">
-        <v>46173.66666666666</v>
+        <v>46173.67708333334</v>
       </c>
     </row>
     <row r="82">
@@ -13398,12 +13398,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13413,12 +13413,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -13445,13 +13445,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>5.77</v>
+        <v>2.16</v>
       </c>
       <c r="O82" t="n">
-        <v>4.8</v>
+        <v>2.77</v>
       </c>
       <c r="P82" t="n">
-        <v>1.47</v>
+        <v>3.63</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -13548,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="AU82" s="3" t="n">
-        <v>46173.67708333334</v>
+        <v>46173.6875</v>
       </c>
     </row>
     <row r="83">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -13604,13 +13604,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="O83" t="n">
-        <v>2.77</v>
+        <v>3.13</v>
       </c>
       <c r="P83" t="n">
-        <v>3.63</v>
+        <v>3.05</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
       <c r="AU83" s="3" t="n">
-        <v>46173.6875</v>
+        <v>46173.70833333334</v>
       </c>
     </row>
     <row r="84">
@@ -13731,12 +13731,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="O84" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="P84" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14193,12 +14193,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -14240,13 +14240,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2.21</v>
+        <v>5.3</v>
       </c>
       <c r="O87" t="n">
-        <v>3.13</v>
+        <v>3.6</v>
       </c>
       <c r="P87" t="n">
-        <v>3.05</v>
+        <v>1.55</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="AU87" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46173.72916666666</v>
       </c>
     </row>
     <row r="88">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -14438,10 +14438,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
       <c r="AU88" s="3" t="n">
-        <v>46173.72916666666</v>
+        <v>46173.76041666666</v>
       </c>
     </row>
     <row r="89">
@@ -14511,12 +14511,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14661,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="AU89" s="3" t="n">
-        <v>46173.76041666666</v>
+        <v>46173.77083333334</v>
       </c>
     </row>
     <row r="90">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -14876,13 +14876,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -14988,12 +14988,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -15035,13 +15035,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -15074,10 +15074,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -15138,7 +15138,7 @@
         <v>0</v>
       </c>
       <c r="AU92" s="3" t="n">
-        <v>46173.77083333334</v>
+        <v>46173.83333333334</v>
       </c>
     </row>
     <row r="93">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15162,12 +15162,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -15306,12 +15306,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15321,12 +15321,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -15456,7 +15456,7 @@
         <v>0</v>
       </c>
       <c r="AU94" s="3" t="n">
-        <v>46173.83333333334</v>
+        <v>46173.84027777778</v>
       </c>
     </row>
     <row r="95">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15551,10 +15551,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -15615,7 +15615,7 @@
         <v>0</v>
       </c>
       <c r="AU95" s="3" t="n">
-        <v>46173.84027777778</v>
+        <v>46173.85416666666</v>
       </c>
     </row>
     <row r="96">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>3.19</v>
+        <v>2.15</v>
       </c>
       <c r="O96" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P96" t="n">
-        <v>2.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="O97" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="P97" t="n">
-        <v>3.54</v>
+        <v>2.76</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15957,12 +15957,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="O98" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P98" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -16028,10 +16028,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16260,12 +16260,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16275,12 +16275,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -16410,165 +16410,6 @@
         <v>0</v>
       </c>
       <c r="AU100" s="3" t="n">
-        <v>46173.85416666666</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Palestino</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU101" s="3" t="n">
         <v>46173.875</v>
       </c>
     </row>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -734,55 +734,55 @@
         <v>4.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>11.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>1.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -3767,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3779,31 +3779,31 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.46</v>
+        <v>2.56</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2.59</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4415,31 +4415,31 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4709,55 +4709,55 @@
         <v>3.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5018,19 +5018,19 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -5039,10 +5039,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -5051,31 +5051,31 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O35" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>5.1</v>
+        <v>3.31</v>
       </c>
       <c r="P36" t="n">
-        <v>8.199999999999999</v>
+        <v>3.27</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3.23</v>
+        <v>2.34</v>
       </c>
       <c r="O39" t="n">
         <v>3.5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.98</v>
+        <v>1.82</v>
       </c>
       <c r="O40" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="P40" t="n">
-        <v>2.13</v>
+        <v>3.13</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O41" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="P41" t="n">
-        <v>3.13</v>
+        <v>2.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.91</v>
+        <v>3.22</v>
       </c>
       <c r="O42" t="n">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="P42" t="n">
-        <v>3.39</v>
+        <v>2.06</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.81</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="P43" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O44" t="n">
-        <v>3.87</v>
+        <v>3.23</v>
       </c>
       <c r="P44" t="n">
-        <v>1.8</v>
+        <v>3.41</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="O45" t="n">
-        <v>5.99</v>
+        <v>5.65</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.83</v>
+        <v>2.92</v>
       </c>
       <c r="O46" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="P46" t="n">
-        <v>4.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.25</v>
+        <v>3.01</v>
       </c>
       <c r="O47" t="n">
-        <v>3.33</v>
+        <v>3.73</v>
       </c>
       <c r="P47" t="n">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="O48" t="n">
-        <v>5.45</v>
+        <v>4.35</v>
       </c>
       <c r="P48" t="n">
-        <v>7.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.43</v>
+        <v>1.96</v>
       </c>
       <c r="O49" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="P49" t="n">
-        <v>2.84</v>
+        <v>3.85</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="O50" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="P50" t="n">
-        <v>5.8</v>
+        <v>4.72</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>5.45</v>
       </c>
       <c r="P52" t="n">
-        <v>3.85</v>
+        <v>7.9</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="O53" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="P53" t="n">
-        <v>4.72</v>
+        <v>3.12</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="O56" t="n">
-        <v>2.95</v>
+        <v>4.55</v>
       </c>
       <c r="P56" t="n">
-        <v>4.96</v>
+        <v>4.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,80 +9470,80 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>3.59</v>
+        <v>1.79</v>
       </c>
       <c r="O57" t="n">
-        <v>4.05</v>
+        <v>2.95</v>
       </c>
       <c r="P57" t="n">
-        <v>1.83</v>
+        <v>4.96</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.95</v>
+        <v>5.45</v>
       </c>
       <c r="AD57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK57" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>0</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.61</v>
+        <v>2.68</v>
       </c>
       <c r="O58" t="n">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="P58" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.68</v>
+        <v>6.34</v>
       </c>
       <c r="O59" t="n">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="P59" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>6.34</v>
+        <v>3.59</v>
       </c>
       <c r="O60" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="P60" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="O61" t="n">
         <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,64 +10265,64 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="O62" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P62" t="n">
-        <v>6.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.44</v>
+        <v>1.5</v>
       </c>
       <c r="O63" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P63" t="n">
-        <v>2.8</v>
+        <v>6.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="O66" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="P66" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O67" t="n">
         <v>3.2</v>
       </c>
       <c r="P67" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="O68" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="P68" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11252,10 +11252,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,64 +11378,64 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="O69" t="n">
-        <v>3.63</v>
+        <v>4.65</v>
       </c>
       <c r="P69" t="n">
-        <v>3.93</v>
+        <v>7.45</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AB69" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11448,10 +11448,10 @@
         </is>
       </c>
       <c r="AJ69" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,64 +11537,64 @@
         </is>
       </c>
       <c r="N70" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O70" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="P70" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y70" t="n">
         <v>1.22</v>
       </c>
-      <c r="O70" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="P70" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="AJ70" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL70" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="O71" t="n">
-        <v>4.65</v>
+        <v>3.37</v>
       </c>
       <c r="P71" t="n">
-        <v>7.45</v>
+        <v>3.44</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11888,10 +11888,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,64 +12014,64 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2.66</v>
+        <v>1.78</v>
       </c>
       <c r="O73" t="n">
-        <v>2.67</v>
+        <v>3.91</v>
       </c>
       <c r="P73" t="n">
-        <v>2.78</v>
+        <v>3.97</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL73" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2.46</v>
+        <v>1.82</v>
       </c>
       <c r="O75" t="n">
-        <v>2.74</v>
+        <v>3.38</v>
       </c>
       <c r="P75" t="n">
-        <v>3.05</v>
+        <v>4.39</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="O77" t="n">
-        <v>3.37</v>
+        <v>2.67</v>
       </c>
       <c r="P77" t="n">
-        <v>3.44</v>
+        <v>2.78</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12767,22 +12767,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,64 +12809,64 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1.78</v>
+        <v>2.76</v>
       </c>
       <c r="O78" t="n">
-        <v>3.91</v>
+        <v>2.68</v>
       </c>
       <c r="P78" t="n">
-        <v>3.97</v>
+        <v>2.68</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.19</v>
+        <v>1.75</v>
       </c>
       <c r="Z78" t="n">
-        <v>4.95</v>
+        <v>1.93</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="AJ78" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -13001,10 +13001,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -13095,12 +13095,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="O80" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P80" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -13890,12 +13890,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -13922,13 +13922,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -14081,13 +14081,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -14717,13 +14717,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -15512,13 +15512,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15798,12 +15798,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -15830,13 +15830,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -15869,10 +15869,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -16148,13 +16148,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>3.19</v>
+        <v>2.64</v>
       </c>
       <c r="O99" t="n">
-        <v>3.29</v>
+        <v>2.96</v>
       </c>
       <c r="P99" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>

--- a/jogos_2026-05-31.xlsx
+++ b/jogos_2026-05-31.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>1.97</v>
       </c>
       <c r="O3" t="n">
         <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>2.84</v>
       </c>
       <c r="O4" t="n">
         <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,19 +2792,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -2813,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2825,31 +2825,31 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3278,55 +3278,55 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>11.2</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2</v>
+        <v>2.59</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>3.18</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U21" t="n">
-        <v>1.95</v>
+        <v>2.69</v>
       </c>
       <c r="V21" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.2</v>
+        <v>3.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.56</v>
+        <v>3.02</v>
       </c>
       <c r="O23" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="P23" t="n">
-        <v>2.59</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="S23" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>3.8</v>
       </c>
       <c r="U23" t="n">
-        <v>2.69</v>
+        <v>2.23</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.38</v>
+        <v>4.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>2.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.02</v>
+        <v>11.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>1.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="V24" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>1.27</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.52</v>
+        <v>1.64</v>
       </c>
       <c r="R27" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="S27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="V27" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.54</v>
+        <v>3.05</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S29" t="n">
         <v>1.27</v>
       </c>
-      <c r="O29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U29" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="V29" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AK29" t="n">
-        <v>3.05</v>
+        <v>1.54</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.72</v>
+        <v>1.35</v>
       </c>
       <c r="O30" t="n">
-        <v>2.81</v>
+        <v>4.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.81</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>1.81</v>
       </c>
       <c r="R30" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="T30" t="n">
-        <v>2.27</v>
+        <v>3.34</v>
       </c>
       <c r="U30" t="n">
-        <v>3.25</v>
+        <v>2.18</v>
       </c>
       <c r="V30" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.49</v>
+        <v>1.12</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.53</v>
+        <v>4.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.41</v>
+        <v>1.52</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.07</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.16</v>
+        <v>1.59</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O36" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="R36" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>2.94</v>
+        <v>3.16</v>
       </c>
       <c r="V36" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.34</v>
+        <v>1.2</v>
       </c>
       <c r="O39" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="P39" t="n">
-        <v>2.13</v>
+        <v>7.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="R39" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="S39" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T39" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="U39" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="V39" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="W39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.14</v>
       </c>
-      <c r="X39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.82</v>
+        <v>2.32</v>
       </c>
       <c r="O40" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="P40" t="n">
-        <v>3.13</v>
+        <v>2.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="R40" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S40" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="T40" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.9</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.88</v>
+        <v>3.22</v>
       </c>
       <c r="O41" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="P41" t="n">
-        <v>2.78</v>
+        <v>2.06</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="R41" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="T41" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="U41" t="n">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="V41" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="W41" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>5</v>
+        <v>3.82</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.66</v>
+        <v>2.21</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.22</v>
+        <v>2.15</v>
       </c>
       <c r="O42" t="n">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="P42" t="n">
-        <v>2.06</v>
+        <v>3.41</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="R42" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.32</v>
       </c>
-      <c r="T42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE42" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>1.26</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="O43" t="n">
-        <v>3.68</v>
+        <v>3.43</v>
       </c>
       <c r="P43" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="R43" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S43" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="T43" t="n">
-        <v>3.98</v>
+        <v>3.44</v>
       </c>
       <c r="U43" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="V43" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="W43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.17</v>
       </c>
-      <c r="X43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z43" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC43" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="O44" t="n">
-        <v>3.23</v>
+        <v>3.47</v>
       </c>
       <c r="P44" t="n">
-        <v>3.41</v>
+        <v>2.78</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R44" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="S44" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="T44" t="n">
-        <v>2.81</v>
+        <v>3.68</v>
       </c>
       <c r="U44" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="V44" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X44" t="n">
         <v>1.03</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z44" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF44" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.97</v>
+        <v>2.66</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="O45" t="n">
-        <v>5.65</v>
+        <v>3.25</v>
       </c>
       <c r="P45" t="n">
-        <v>7.3</v>
+        <v>3.13</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="R45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T45" t="n">
         <v>2.9</v>
       </c>
-      <c r="S45" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4.45</v>
-      </c>
       <c r="U45" t="n">
-        <v>1.88</v>
+        <v>2.59</v>
       </c>
       <c r="V45" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="W45" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z45" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AB45" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK45" t="n">
-        <v>3.3</v>
+        <v>1.91</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="O46" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="P46" t="n">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
         <v>2.45</v>
       </c>
       <c r="S46" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T46" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U46" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="V46" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W46" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X46" t="n">
         <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="O47" t="n">
-        <v>3.73</v>
+        <v>3.55</v>
       </c>
       <c r="P47" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.49</v>
+        <v>2.43</v>
       </c>
       <c r="O48" t="n">
-        <v>4.35</v>
+        <v>3.31</v>
       </c>
       <c r="P48" t="n">
-        <v>5.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="O49" t="n">
-        <v>3.34</v>
+        <v>4.35</v>
       </c>
       <c r="P49" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8366,34 +8366,34 @@
         <v>4.72</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA50" t="n">
         <v>1.84</v>
@@ -8402,19 +8402,19 @@
         <v>1.94</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8684,55 +8684,55 @@
         <v>7.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="O53" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="P53" t="n">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,64 +9470,64 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.79</v>
+        <v>6.34</v>
       </c>
       <c r="O57" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="P57" t="n">
-        <v>4.96</v>
+        <v>1.41</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.68</v>
+        <v>1.79</v>
       </c>
       <c r="O58" t="n">
-        <v>3.68</v>
+        <v>2.95</v>
       </c>
       <c r="P58" t="n">
-        <v>2.3</v>
+        <v>4.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>6.34</v>
+        <v>2.68</v>
       </c>
       <c r="O59" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="P59" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,64 +10265,64 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="O62" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P62" t="n">
-        <v>2.75</v>
+        <v>6.55</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="O63" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P63" t="n">
-        <v>6.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="O66" t="n">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O67" t="n">
         <v>3.2</v>
       </c>
       <c r="P67" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="O68" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="P68" t="n">
-        <v>4.2</v>
+        <v>7.45</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -11336,22 +11336,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -11378,64 +11378,64 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="O69" t="n">
-        <v>4.65</v>
+        <v>3.63</v>
       </c>
       <c r="P69" t="n">
-        <v>7.45</v>
+        <v>3.93</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11448,10 +11448,10 @@
         </is>
       </c>
       <c r="AJ69" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL69" t="n">
         <v>0</v>
@@ -11495,22 +11495,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -11537,64 +11537,64 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="AJ70" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK70" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL70" t="n">
         <v>0</v>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="O71" t="n">
-        <v>3.37</v>
+        <v>6.3</v>
       </c>
       <c r="P71" t="n">
-        <v>3.44</v>
+        <v>16</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -11823,12 +11823,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -11855,13 +11855,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -12014,64 +12014,64 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="O73" t="n">
-        <v>3.91</v>
+        <v>2.64</v>
       </c>
       <c r="P73" t="n">
-        <v>3.97</v>
+        <v>3.55</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.19</v>
+        <v>1.72</v>
       </c>
       <c r="Z73" t="n">
-        <v>4.95</v>
+        <v>1.97</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12084,10 +12084,10 @@
         </is>
       </c>
       <c r="AJ73" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL73" t="n">
         <v>0</v>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -12173,64 +12173,64 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="O74" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="P74" t="n">
-        <v>3.69</v>
+        <v>2.78</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12243,10 +12243,10 @@
         </is>
       </c>
       <c r="AJ74" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK74" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL74" t="n">
         <v>0</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12300,12 +12300,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1.82</v>
+        <v>2.46</v>
       </c>
       <c r="O75" t="n">
-        <v>3.38</v>
+        <v>2.74</v>
       </c>
       <c r="P75" t="n">
-        <v>4.39</v>
+        <v>3.05</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -12459,12 +12459,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -12491,64 +12491,64 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="O76" t="n">
         <v>2.74</v>
       </c>
       <c r="P76" t="n">
-        <v>3.05</v>
+        <v>3.69</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12561,10 +12561,10 @@
         </is>
       </c>
       <c r="AJ76" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK76" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL76" t="n">
         <v>0</v>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -12650,13 +12650,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O77" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="P77" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -12683,10 +12683,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -12767,22 +12767,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -12809,64 +12809,64 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2.76</v>
+        <v>1.78</v>
       </c>
       <c r="O78" t="n">
-        <v>2.68</v>
+        <v>3.91</v>
       </c>
       <c r="P78" t="n">
-        <v>2.68</v>
+        <v>3.97</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.75</v>
+        <v>1.19</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.93</v>
+        <v>4.95</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL78" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="E79" t="inlineStr">
       